--- a/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
+++ b/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:I253"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1633,7 +1633,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].text</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal._default[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1643,24 +1643,29 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].text</t>
+          <t xml:space="preserve">normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🔥 苦しい中でもチームの結束が深まった</t>
+          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].detail</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal._default[2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1670,24 +1675,29 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].detail</t>
+          <t xml:space="preserve">normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">資金繰りは厳しいが、選手たちの表情に迷いはない。困難を共にすることで、絆が強まっているようだ。</t>
+          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].text</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal._default[3]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1697,24 +1707,29 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].text</t>
+          <t xml:space="preserve">normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💪 逆境がチームを強くしている</t>
+          <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].detail</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.bold._default[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1724,24 +1739,29 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].detail</t>
+          <t xml:space="preserve">bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">豪華な設備も潤沢な資金もない。だからこそ、選手同士で支え合う文化が自然に生まれている。</t>
+          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].text</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.bold._default[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -1751,24 +1771,29 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].text</t>
+          <t xml:space="preserve">bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🤝 厳しい時期だからこそ仲間の大切さを実感</t>
+          <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].detail</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet._default[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -1778,24 +1803,29 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].detail</t>
+          <t xml:space="preserve">quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決して恵まれた環境ではない。それでも、誰一人として文句を言わずに練習に打ち込む姿がある。</t>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].text</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet._default[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -1805,24 +1835,29 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].text</t>
+          <t xml:space="preserve">quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">✊ チーム全員が同じ方向を向いている</t>
+          <t xml:space="preserve">…がんばります。…それだけ、です</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].detail</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.shy._default[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -1832,24 +1867,29 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].detail</t>
+          <t xml:space="preserve">shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">苦しい状況を全員で分かち合っている。この経験が、いつかチームの財産になるはずだ。</t>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.shy._default[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -1859,24 +1899,29 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mild[1]</t>
+          <t xml:space="preserve">shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ 業界筋が{name}の試合映像を取り寄せているらしい</t>
+          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -1886,24 +1931,29 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mild[2]</t>
+          <t xml:space="preserve">easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {name}の名前が他団体の会議で挙がっていたとの噂</t>
+          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、あたし</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[3]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing._default[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -1913,24 +1963,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mild[3]</t>
+          <t xml:space="preserve">easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {name}への注目度が他団体内で高まっているようだ</t>
+          <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest._default[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -1940,24 +1995,29 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[1]</t>
+          <t xml:space="preserve">earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {rival}のスカウトが{name}の試合をチェックしていた</t>
+          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest._default[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -1967,24 +2027,29 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[2]</t>
+          <t xml:space="preserve">earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {rival}関係者が{name}について詳しく探っているらしい</t>
+          <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[3]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional._default[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -1994,24 +2059,29 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[3]</t>
+          <t xml:space="preserve">emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ 業界紙が{name}を「動向注目の選手」として取り上げた</t>
+          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional._default[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2021,24 +2091,29 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">serious[1]</t>
+          <t xml:space="preserve">emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ 複数の団体が{name}に接触を試みている噂が流れている</t>
+          <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2048,24 +2123,24 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">serious[2]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}の周辺で他団体の動きが活発化している</t>
+          <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[3]</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2075,24 +2150,24 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">serious[3]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}への具体的なオファーが近いとの観測が出ている</t>
+          <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2102,24 +2177,24 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[1]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 ロッカールームから笑い声が聞こえてくる</t>
+          <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.normal._default[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2129,24 +2204,29 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[2]</t>
+          <t xml:space="preserve">normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 控室の空気は和やかだ</t>
+          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[3]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.normal._default[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2156,24 +2236,29 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[3]</t>
+          <t xml:space="preserve">normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 選手たちが自主練で残っている</t>
+          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[4]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.normal._default[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2183,24 +2268,29 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[4]</t>
+          <t xml:space="preserve">normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 誰かが差し入れを持ってきたらしい</t>
+          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.bold._default[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2210,24 +2300,29 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[1]</t>
+          <t xml:space="preserve">bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 控室で{name}がため息をついていた</t>
+          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.bold._default[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2237,24 +2332,29 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[2]</t>
+          <t xml:space="preserve">bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}の表情が最近硬い</t>
+          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[3]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.quiet._default[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2264,24 +2364,29 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[3]</t>
+          <t xml:space="preserve">quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 ロッカーの会話が少ない日が続いている</t>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[4]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.quiet._default[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2291,24 +2396,29 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[4]</t>
+          <t xml:space="preserve">quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}が一人で帰る姿を見かけた</t>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[5]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.shy._default[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2318,24 +2428,29 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[5]</t>
+          <t xml:space="preserve">shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 練習後、{name}がスマホをじっと見つめていた</t>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.shy._default[2]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2345,24 +2460,29 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[1]</t>
+          <t xml:space="preserve">shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 ロッカールームの空気が重い</t>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2372,24 +2492,29 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[2]</t>
+          <t xml:space="preserve">easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}と{name2}が何か話し込んでいた</t>
+          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[3]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing._default[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2399,24 +2524,29 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[3]</t>
+          <t xml:space="preserve">easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 控室で小さな言い争いがあったらしい</t>
+          <t xml:space="preserve">声かかんなくてさー。拾ってくれて助かったよ</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[4]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.earnest._default[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2426,24 +2556,29 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[4]</t>
+          <t xml:space="preserve">earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}の機嫌が明らかに悪い</t>
+          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[5]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.earnest._default[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2453,24 +2588,29 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[5]</t>
+          <t xml:space="preserve">earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 誰もが口数少なく着替えを済ませていた</t>
+          <t xml:space="preserve">拾ってくれた恩は、練習の量でお返しします</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][1].text</t>
+          <t xml:space="preserve">FA_GREETING_LINES.emotional._default[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2480,24 +2620,29 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1][1].text</t>
+          <t xml:space="preserve">emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場が静まり返っている</t>
+          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][2].text</t>
+          <t xml:space="preserve">FA_GREETING_LINES.emotional._default[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2507,24 +2652,29 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1][2].text</t>
+          <t xml:space="preserve">emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰も目を合わせようとしない</t>
+          <t xml:space="preserve">拾ってくれた…！この恩、絶対に返す…！</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][3].text</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2534,24 +2684,24 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1][3].text</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重い空気が漂っている</t>
+          <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][1].text</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2561,24 +2711,24 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][1].text</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこかよそよそしい空気がある</t>
+          <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][2].text</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[3]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2588,24 +2738,24 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][2].text</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最低限のメニューだけこなしている</t>
+          <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][3].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].text</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2615,24 +2765,24 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][3].text</t>
+          <t xml:space="preserve">[1].text</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">会話が少ない</t>
+          <t xml:space="preserve">🔥 苦しい中でもチームの結束が深まった</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][1].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].detail</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -2642,24 +2792,24 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][1].text</t>
+          <t xml:space="preserve">[1].detail</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">淡々とメニューをこなしている</t>
+          <t xml:space="preserve">資金繰りは厳しいが、選手たちの表情に迷いはない。困難を共にすることで、絆が強まっているようだ。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][2].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].text</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -2669,24 +2819,24 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][2].text</t>
+          <t xml:space="preserve">[2].text</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りの練習風景</t>
+          <t xml:space="preserve">💪 逆境がチームを強くしている</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][3].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].detail</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -2696,24 +2846,24 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][3].text</t>
+          <t xml:space="preserve">[2].detail</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特に変わった様子はない</t>
+          <t xml:space="preserve">豪華な設備も潤沢な資金もない。だからこそ、選手同士で支え合う文化が自然に生まれている。</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][4].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].text</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -2723,24 +2873,24 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][4].text</t>
+          <t xml:space="preserve">[3].text</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙々と汗を流している</t>
+          <t xml:space="preserve">🤝 厳しい時期だからこそ仲間の大切さを実感</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][1].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].detail</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -2750,24 +2900,24 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][1].text</t>
+          <t xml:space="preserve">[3].detail</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声が飛び交っている</t>
+          <t xml:space="preserve">決して恵まれた環境ではない。それでも、誰一人として文句を言わずに練習に打ち込む姿がある。</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][2].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].text</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -2777,24 +2927,24 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][2].text</t>
+          <t xml:space="preserve">[4].text</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習に熱が入っている</t>
+          <t xml:space="preserve">✊ チーム全員が同じ方向を向いている</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][3].text</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].detail</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -2804,24 +2954,24 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][3].text</t>
+          <t xml:space="preserve">[4].detail</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手同士でアドバイスし合っている</t>
+          <t xml:space="preserve">苦しい状況を全員で分かち合っている。この経験が、いつかチームの財産になるはずだ。</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][4].text</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.title</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -2831,24 +2981,24 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][4].text</t>
+          <t xml:space="preserve">pyrrhic.title</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活気のある練習場</t>
+          <t xml:space="preserve">勝 者 の 代 償</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][1].text</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.lead</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -2858,24 +3008,24 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][1].text</t>
+          <t xml:space="preserve">pyrrhic.lead</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自主練する選手が増えている</t>
+          <t xml:space="preserve">その試合に、彼女は勝った。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][2].text</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.body</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -2885,24 +3035,24 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][2].text</t>
+          <t xml:space="preserve">pyrrhic.body</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場に笑い声が響いている</t>
+          <t xml:space="preserve">勝ち名乗りを受けることは、なかった。担架が運び込まれ、歓声が戸惑いに変わっていく。後日、医師の所見が団体に届いた。もうリングには上がれない、と。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][3].text</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.title</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -2912,24 +3062,24 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][3].text</t>
+          <t xml:space="preserve">defended.title</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員の目つきが違う</t>
+          <t xml:space="preserve">王 座 を 守 っ て</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][4].text</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.lead</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -2939,1656 +3089,1401 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][4].text</t>
+          <t xml:space="preserve">defended.lead</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チーム全体に勢いがある</t>
+          <t xml:space="preserve">ベルトは、守った。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.normal</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.body</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.normal</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">defended.body</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
+          <t xml:space="preserve">防衛を告げるゴングの直後、王者はマットに崩れ落ちた。巻いたまま運ばれていく背中を、会場の誰もが見送るしかなかった。数日後、王座は返上されることになる。</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.ojousama</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.title</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.ojousama</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">neverCrowned.title</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
+          <t xml:space="preserve">冠 に 届 か ず</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.delinquent</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.lead</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.delinquent</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">neverCrowned.lead</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
+          <t xml:space="preserve">あと一歩が、遠かった。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.cool</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.body</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.cool</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">neverCrowned.body</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
+          <t xml:space="preserve">挑戦は実らず、そしてそれが最後の試合になった。結局、彼女は一度もベルトを腰に巻かないまま去ることになる。記録に残るのは、挑戦者としての名前だけだ。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.seductive</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.title</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.seductive</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">burntOut.title</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
+          <t xml:space="preserve">追 い 込 み の ツ ケ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.polite</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.lead</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.polite</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">burntOut.lead</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
+          <t xml:space="preserve">その体は、とうに限界を過ぎていた。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.composed</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.body</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.composed</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">burntOut.body</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
+          <t xml:space="preserve">若い頃から追い込みを重ねた体だった。踏ん張りが効かず、崩れるように倒れた。請求書は、忘れた頃に届く。今日がその日だった。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.normal</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.title</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.normal</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">lastWin.title</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
+          <t xml:space="preserve">最 後 の 一 勝</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.ojousama</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.lead</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.ojousama</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">lastWin.lead</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
+          <t xml:space="preserve">引退を表明していた。その最後の一勝だった。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.delinquent</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.body</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.delinquent</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">lastWin.body</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
+          <t xml:space="preserve">勝った直後に、彼女は動けなくなった。予定されていた引退試合は、もう組めない。花道は、その途中で終わった。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.cool</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.cool</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">mild[1]</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
+          <t xml:space="preserve">👁️ 業界筋が{name}の試合映像を取り寄せているらしい</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.seductive</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.seductive</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">mild[2]</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
+          <t xml:space="preserve">👁️ {name}の名前が他団体の会議で挙がっていたとの噂</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.polite</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[3]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.polite</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">mild[3]</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">競い合えることが、自分の力になっています</t>
+          <t xml:space="preserve">👁️ {name}への注目度が他団体内で高まっているようだ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.composed</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.composed</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">moderate[1]</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
+          <t xml:space="preserve">👁️ {rival}のスカウトが{name}の試合をチェックしていた</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.normal</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[2]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.normal</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">moderate[2]</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
+          <t xml:space="preserve">👁️ {rival}関係者が{name}について詳しく探っているらしい</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.ojousama</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[3]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.ojousama</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">moderate[3]</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
+          <t xml:space="preserve">👁️ 業界紙が{name}を「動向注目の選手」として取り上げた</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.delinquent</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.delinquent</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">serious[1]</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
+          <t xml:space="preserve">⚠️ 複数の団体が{name}に接触を試みている噂が流れている</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.cool</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.cool</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">serious[2]</t>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
+          <t xml:space="preserve">⚠️ {name}の周辺で他団体の動きが活発化している</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.seductive</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[3]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.seductive</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">serious[3]</t>
         </is>
       </c>
       <c r="G120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
+          <t xml:space="preserve">⚠️ {name}への具体的なオファーが近いとの観測が出ている</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.polite</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.polite</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">good[1]</t>
         </is>
       </c>
       <c r="G121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
+          <t xml:space="preserve">💬 ロッカールームから笑い声が聞こえてくる</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.composed</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[2]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.composed</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">good[2]</t>
         </is>
       </c>
       <c r="G122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
+          <t xml:space="preserve">💬 控室の空気は和やかだ</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.normal</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[3]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.normal</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">good[3]</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
+          <t xml:space="preserve">💬 選手たちが自主練で残っている</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.ojousama</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[4]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.ojousama</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">good[4]</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
+          <t xml:space="preserve">💬 誰かが差し入れを持ってきたらしい</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.delinquent</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.delinquent</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">warning[1]</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
+          <t xml:space="preserve">💬 控室で{name}がため息をついていた</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.cool</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.cool</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">warning[2]</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
+          <t xml:space="preserve">💬 {name}の表情が最近硬い</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.seductive</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[3]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.seductive</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">warning[3]</t>
         </is>
       </c>
       <c r="G127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
+          <t xml:space="preserve">💬 ロッカーの会話が少ない日が続いている</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.polite</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[4]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.polite</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">warning[4]</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
+          <t xml:space="preserve">💬 {name}が一人で帰る姿を見かけた</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.composed</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[5]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.composed</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">warning[5]</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
+          <t xml:space="preserve">💬 練習後、{name}がスマホをじっと見つめていた</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.normal</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.normal</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">danger[1]</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
+          <t xml:space="preserve">💬 ロッカールームの空気が重い</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.ojousama</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[2]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.ojousama</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">danger[2]</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
+          <t xml:space="preserve">💬 {name}と{name2}が何か話し込んでいた</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.delinquent</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[3]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.delinquent</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">danger[3]</t>
         </is>
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
+          <t xml:space="preserve">💬 控室で小さな言い争いがあったらしい</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.cool</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[4]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.cool</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">danger[4]</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気にしていないつもりだった……</t>
+          <t xml:space="preserve">💬 {name}の機嫌が明らかに悪い</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.seductive</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[5]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.seductive</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">danger[5]</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
+          <t xml:space="preserve">💬 誰もが口数少なく着替えを済ませていた</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.polite</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][1].text</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.polite</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[1][1].text</t>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
+          <t xml:space="preserve">練習場が静まり返っている</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.composed</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][2].text</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.composed</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[1][2].text</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
+          <t xml:space="preserve">誰も目を合わせようとしない</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.normal</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][3].text</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.normal</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">[1][3].text</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
+          <t xml:space="preserve">重い空気が漂っている</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.ojousama</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][1].text</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.ojousama</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">[2][1].text</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
+          <t xml:space="preserve">どこかよそよそしい空気がある</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.delinquent</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][2].text</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.delinquent</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">[2][2].text</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
+          <t xml:space="preserve">最低限のメニューだけこなしている</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.cool</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][3].text</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.cool</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">[2][3].text</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
+          <t xml:space="preserve">会話が少ない</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.seductive</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][1].text</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.seductive</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">[3][1].text</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
+          <t xml:space="preserve">淡々とメニューをこなしている</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.polite</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][2].text</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.polite</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[3][2].text</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
+          <t xml:space="preserve">いつも通りの練習風景</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.composed</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][3].text</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.composed</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[3][3].text</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
+          <t xml:space="preserve">特に変わった様子はない</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.normal</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][4].text</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.normal</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">[3][4].text</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
+          <t xml:space="preserve">黙々と汗を流している</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.ojousama</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][1].text</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.ojousama</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">[4][1].text</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
+          <t xml:space="preserve">声が飛び交っている</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.delinquent</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][2].text</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.delinquent</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">[4][2].text</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いたな。それで?</t>
+          <t xml:space="preserve">練習に熱が入っている</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.cool</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][3].text</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.cool</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">[4][3].text</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認識しているだけ。それ以上はない</t>
+          <t xml:space="preserve">選手同士でアドバイスし合っている</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.seductive</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][4].text</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.seductive</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">[4][4].text</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
+          <t xml:space="preserve">活気のある練習場</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.polite</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][1].text</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.polite</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[5][1].text</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますけれど、特には……</t>
+          <t xml:space="preserve">自主練する選手が増えている</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.composed</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][2].text</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.composed</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[5][2].text</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
+          <t xml:space="preserve">練習場に笑い声が響いている</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.normal</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][3].text</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.normal</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">[5][3].text</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
+          <t xml:space="preserve">全員の目つきが違う</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.ojousama</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][4].text</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.ojousama</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">[5][4].text</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
+          <t xml:space="preserve">チーム全体に勢いがある</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.normal</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4603,24 +4498,24 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.delinquent</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">trust.normal</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
+          <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.ojousama</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4635,24 +4530,24 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.cool</t>
+          <t xml:space="preserve">trust.ojousama</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
+          <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.delinquent</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -4667,24 +4562,24 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.seductive</t>
+          <t xml:space="preserve">trust.delinquent</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
+          <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.cool</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -4699,24 +4594,24 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.polite</t>
+          <t xml:space="preserve">trust.cool</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
+          <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.seductive</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -4731,24 +4626,24 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.composed</t>
+          <t xml:space="preserve">trust.seductive</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
+          <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.polite</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -4763,24 +4658,24 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.normal</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">trust.polite</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
+          <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.composed</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -4795,24 +4690,24 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.ojousama</t>
+          <t xml:space="preserve">trust.composed</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
+          <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.normal</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -4827,24 +4722,24 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.delinquent</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">rival_friend.normal</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
+          <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.ojousama</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -4859,24 +4754,24 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.cool</t>
+          <t xml:space="preserve">rival_friend.ojousama</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不快。距離を取りたい</t>
+          <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.delinquent</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -4891,24 +4786,24 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.seductive</t>
+          <t xml:space="preserve">rival_friend.delinquent</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
+          <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.cool</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -4923,24 +4818,24 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.polite</t>
+          <t xml:space="preserve">rival_friend.cool</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
+          <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.seductive</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -4955,24 +4850,24 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.composed</t>
+          <t xml:space="preserve">rival_friend.seductive</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
+          <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.polite</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -4987,24 +4882,24 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.normal</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">rival_friend.polite</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
+          <t xml:space="preserve">競い合えることが、自分の力になっています</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.composed</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5019,24 +4914,24 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.ojousama</t>
+          <t xml:space="preserve">rival_friend.composed</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
+          <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.normal</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5051,24 +4946,24 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.delinquent</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">destined_rival.normal</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
+          <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.ojousama</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5083,24 +4978,24 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.cool</t>
+          <t xml:space="preserve">destined_rival.ojousama</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受け付けない。理屈じゃない</t>
+          <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.delinquent</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5115,24 +5010,24 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.seductive</t>
+          <t xml:space="preserve">destined_rival.delinquent</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
+          <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.cool</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5147,24 +5042,24 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.polite</t>
+          <t xml:space="preserve">destined_rival.cool</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
+          <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.seductive</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5179,24 +5074,24 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.composed</t>
+          <t xml:space="preserve">destined_rival.seductive</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
+          <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.polite</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5211,24 +5106,24 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.normal</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">destined_rival.polite</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
+          <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.composed</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5243,24 +5138,24 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.ojousama</t>
+          <t xml:space="preserve">destined_rival.composed</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
+          <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.normal</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5275,24 +5170,24 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.delinquent</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">acquaintance.normal</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
+          <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.ojousama</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5307,24 +5202,24 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.cool</t>
+          <t xml:space="preserve">acquaintance.ojousama</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存在を認識から外している。話すこともない</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.delinquent</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5339,24 +5234,24 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.seductive</t>
+          <t xml:space="preserve">acquaintance.delinquent</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
+          <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.cool</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5371,24 +5266,24 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.polite</t>
+          <t xml:space="preserve">acquaintance.cool</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
+          <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.seductive</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5403,24 +5298,24 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.composed</t>
+          <t xml:space="preserve">acquaintance.seductive</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
+          <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.polite</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5435,24 +5330,24 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.normal</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">acquaintance.polite</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
+          <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.composed</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5467,24 +5362,24 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.ojousama</t>
+          <t xml:space="preserve">acquaintance.composed</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
+          <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.normal</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5499,24 +5394,24 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.delinquent</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">intrigued.normal</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
+          <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.ojousama</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5531,24 +5426,24 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.cool</t>
+          <t xml:space="preserve">intrigued.ojousama</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">生理的に駄目。これは変わらない</t>
+          <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.delinquent</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -5563,24 +5458,24 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.seductive</t>
+          <t xml:space="preserve">intrigued.delinquent</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
+          <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.cool</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5595,24 +5490,24 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.polite</t>
+          <t xml:space="preserve">intrigued.cool</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
+          <t xml:space="preserve">気にしていないつもりだった……</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.seductive</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5627,24 +5522,24 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.composed</t>
+          <t xml:space="preserve">intrigued.seductive</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
+          <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.polite</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5659,24 +5554,24 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.normal</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">intrigued.polite</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
+          <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.composed</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -5691,24 +5586,24 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.ojousama</t>
+          <t xml:space="preserve">intrigued.composed</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
+          <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.normal</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -5723,24 +5618,24 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.delinquent</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">hostile_competitor.normal</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
+          <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.ojousama</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -5755,24 +5650,24 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.cool</t>
+          <t xml:space="preserve">hostile_competitor.ojousama</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
+          <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.delinquent</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -5787,24 +5682,24 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.seductive</t>
+          <t xml:space="preserve">hostile_competitor.delinquent</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
+          <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.cool</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -5819,24 +5714,24 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.polite</t>
+          <t xml:space="preserve">hostile_competitor.cool</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
+          <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.seductive</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -5851,292 +5746,1924 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.composed</t>
+          <t xml:space="preserve">hostile_competitor.seductive</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
+          <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[1].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.polite</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].label</t>
+          <t xml:space="preserve">hostile_competitor.polite</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">初興行収入</t>
+          <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[1].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.composed</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].desc</t>
+          <t xml:space="preserve">hostile_competitor.composed</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
+          <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[2].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.normal</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].label</t>
+          <t xml:space="preserve">distant.normal</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スポンサー獲得</t>
+          <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[2].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.ojousama</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].desc</t>
+          <t xml:space="preserve">distant.ojousama</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[3].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.delinquent</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].label</t>
+          <t xml:space="preserve">distant.delinquent</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">初の月次黒字</t>
+          <t xml:space="preserve">あー、いたな。それで?</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[3].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.cool</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].desc</t>
+          <t xml:space="preserve">distant.cool</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
+          <t xml:space="preserve">認識しているだけ。それ以上はない</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[4].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.seductive</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].label</t>
+          <t xml:space="preserve">distant.seductive</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2ヶ月連続月次黒字</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[4].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.polite</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].desc</t>
+          <t xml:space="preserve">distant.polite</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">安定経営が見えてきた</t>
+          <t xml:space="preserve">お見かけはしますけれど、特には……</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[5].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.composed</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5].label</t>
+          <t xml:space="preserve">distant.composed</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">経営安定化</t>
+          <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.normal</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.normal</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.ojousama</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.ojousama</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.delinquent</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.delinquent</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.cool</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.cool</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.seductive</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.seductive</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.polite</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.polite</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.composed</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">contempt.composed</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.normal</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.normal</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.ojousama</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.ojousama</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.delinquent</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.delinquent</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.cool</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.cool</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">不快。距離を取りたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.seductive</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.seductive</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.polite</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.polite</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.composed</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">irritation.composed</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.normal</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.normal</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.ojousama</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.ojousama</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.delinquent</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.delinquent</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.cool</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.cool</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受け付けない。理屈じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.seductive</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.seductive</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.polite</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.polite</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.composed</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike.composed</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.normal</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.normal</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.ojousama</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.ojousama</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.delinquent</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.delinquent</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.cool</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.cool</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">存在を認識から外している。話すこともない</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.seductive</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.seductive</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.polite</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.polite</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.composed</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cold_loathing.composed</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.normal</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.normal</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.ojousama</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.ojousama</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.delinquent</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.delinquent</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.cool</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.cool</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">生理的に駄目。これは変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.seductive</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.seductive</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.polite</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.polite</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.composed</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">dislike_strong.composed</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.normal</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.normal</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.ojousama</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.ojousama</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.delinquent</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.delinquent</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.cool</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.cool</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.seductive</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.seductive</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.polite</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.polite</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.composed</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.composed</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[1].label</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[1].label</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">初興行収入</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[1].desc</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[1].desc</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[2].label</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[2].label</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">スポンサー獲得</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[2].desc</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[2].desc</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[3].label</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[3].label</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">初の月次黒字</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[3].desc</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[3].desc</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[4].label</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[4].label</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2ヶ月連続月次黒字</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[4].desc</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[4].desc</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">安定経営が見えてきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[5].label</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[5].label</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">経営安定化</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES[5].desc</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr" s="2">
+      <c r="B253" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr" s="2">
+      <c r="C253" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr" s="12">
+      <c r="D253" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5].desc</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr" s="3">
+      <c r="G253" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">月次黒字定着＋資金確保！サバイバルクリア</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I202"/>
+  <autoFilter ref="A1:I253"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
+++ b/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
@@ -4483,7 +4483,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.standard</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.normal</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">trust.standard</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
@@ -4707,7 +4707,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.standard</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -4722,12 +4722,12 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.normal</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">rival_friend.standard</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
@@ -4931,7 +4931,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.standard</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.normal</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">destined_rival.standard</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
@@ -5155,7 +5155,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.standard</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.normal</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">acquaintance.standard</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
@@ -5379,7 +5379,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.standard</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.normal</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">intrigued.standard</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="3">
@@ -5603,7 +5603,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.standard</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.normal</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">hostile_competitor.standard</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
@@ -5827,7 +5827,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.standard</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.normal</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">distant.standard</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="3">
@@ -6051,7 +6051,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.standard</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.normal</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">contempt.standard</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G202" t="inlineStr" s="3">
@@ -6275,7 +6275,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.standard</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.normal</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">irritation.standard</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="3">
@@ -6499,7 +6499,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.standard</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.normal</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">dislike.standard</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G216" t="inlineStr" s="3">
@@ -6723,7 +6723,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.standard</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.normal</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">cold_loathing.standard</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G223" t="inlineStr" s="3">
@@ -6947,7 +6947,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.standard</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.normal</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">dislike_strong.standard</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G230" t="inlineStr" s="3">
@@ -7171,7 +7171,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.normal</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.standard</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.normal</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">hatred.standard</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G237" t="inlineStr" s="3">

--- a/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
+++ b/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
@@ -1633,7 +1633,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="5">
@@ -1665,7 +1665,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="5">
@@ -1697,7 +1697,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal._default[3]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="5">
@@ -1729,7 +1729,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="6">
@@ -1761,7 +1761,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="6">
@@ -1793,7 +1793,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="7">
@@ -1825,7 +1825,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="7">
@@ -1857,7 +1857,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.shy._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="8">
@@ -1889,7 +1889,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.shy._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="8">
@@ -1921,7 +1921,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="9">
@@ -1953,7 +1953,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="9">
@@ -1985,7 +1985,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="10">
@@ -2017,7 +2017,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="10">
@@ -2049,7 +2049,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="10">
@@ -2081,7 +2081,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="10">
@@ -2194,7 +2194,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="5">
@@ -2226,7 +2226,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="5">
@@ -2258,7 +2258,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal._default[3]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="5">
@@ -2290,7 +2290,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="6">
@@ -2322,7 +2322,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="6">
@@ -2354,7 +2354,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="7">
@@ -2386,7 +2386,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="7">
@@ -2418,7 +2418,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.shy._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="8">
@@ -2450,7 +2450,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.shy._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="8">
@@ -2482,7 +2482,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="9">
@@ -2514,7 +2514,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="9">
@@ -2546,7 +2546,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="10">
@@ -2578,7 +2578,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="10">
@@ -2610,7 +2610,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="10">
@@ -2642,7 +2642,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="10">

--- a/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
+++ b/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I253"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1633,7 +1633,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.normal[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1643,29 +1643,24 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+          <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.normal[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1675,29 +1670,24 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+          <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.normal[3]</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[3]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1707,29 +1697,24 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.normal[3]</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
+          <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.bold[1]</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1739,29 +1724,24 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+          <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.bold[2]</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -1771,29 +1751,24 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
+          <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.quiet[1]</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[3]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -1803,29 +1778,24 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.quiet[1]</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+          <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.quiet[2]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].text</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -1835,29 +1805,24 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.quiet[2]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">[1].text</t>
         </is>
       </c>
       <c r="G59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…がんばります。…それだけ、です</t>
+          <t xml:space="preserve">🔥 苦しい中でもチームの結束が深まった</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.shy[1]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].detail</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -1867,29 +1832,24 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.shy[1]</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">[1].detail</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+          <t xml:space="preserve">資金繰りは厳しいが、選手たちの表情に迷いはない。困難を共にすることで、絆が強まっているようだ。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.shy[2]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].text</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -1899,29 +1859,24 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.shy[2]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">[2].text</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
+          <t xml:space="preserve">💪 逆境がチームを強くしている</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.easygoing[1]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].detail</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -1931,29 +1886,24 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">[2].detail</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、あたし</t>
+          <t xml:space="preserve">豪華な設備も潤沢な資金もない。だからこそ、選手同士で支え合う文化が自然に生まれている。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.easygoing[2]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].text</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -1963,29 +1913,24 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.easygoing[2]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">[3].text</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
+          <t xml:space="preserve">🤝 厳しい時期だからこそ仲間の大切さを実感</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.earnest[1]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].detail</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -1995,29 +1940,24 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">[3].detail</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+          <t xml:space="preserve">決して恵まれた環境ではない。それでも、誰一人として文句を言わずに練習に打ち込む姿がある。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.earnest[2]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].text</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2027,29 +1967,24 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">[4].text</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
+          <t xml:space="preserve">✊ チーム全員が同じ方向を向いている</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.emotional[1]</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].detail</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2059,29 +1994,24 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">[4].detail</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+          <t xml:space="preserve">苦しい状況を全員で分かち合っている。この経験が、いつかチームの財産になるはずだ。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES._default.emotional[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.title</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2091,29 +2021,24 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">pyrrhic.title</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
+          <t xml:space="preserve">勝 者 の 代 償</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[1]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.lead</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2123,24 +2048,24 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">pyrrhic.lead</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
+          <t xml:space="preserve">その試合に、彼女は勝った。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.body</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2150,24 +2075,24 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">pyrrhic.body</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
+          <t xml:space="preserve">勝ち名乗りを受けることは、なかった。担架が運び込まれ、歓声が戸惑いに変わっていく。後日、医師の所見が団体に届いた。もうリングには上がれない、と。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES[3]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.title</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2177,24 +2102,24 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">defended.title</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
+          <t xml:space="preserve">王 座 を 守 っ て</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.normal[1]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.lead</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2204,29 +2129,24 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">defended.lead</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
+          <t xml:space="preserve">ベルトは、守った。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.normal[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.body</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2236,29 +2156,24 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">defended.body</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
+          <t xml:space="preserve">防衛を告げるゴングの直後、王者はマットに崩れ落ちた。巻いたまま運ばれていく背中を、会場の誰もが見送るしかなかった。数日後、王座は返上されることになる。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.normal[3]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.title</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2268,29 +2183,24 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.normal[3]</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">neverCrowned.title</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
+          <t xml:space="preserve">冠 に 届 か ず</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.bold[1]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.lead</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2300,29 +2210,24 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">neverCrowned.lead</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
+          <t xml:space="preserve">あと一歩が、遠かった。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.bold[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.body</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2332,29 +2237,24 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">neverCrowned.body</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+          <t xml:space="preserve">挑戦は実らず、そしてそれが最後の試合になった。結局、彼女は一度もベルトを腰に巻かないまま去ることになる。記録に残るのは、挑戦者としての名前だけだ。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.quiet[1]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.title</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2364,29 +2264,24 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.quiet[1]</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">burntOut.title</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+          <t xml:space="preserve">追 い 込 み の ツ ケ</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.quiet[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.lead</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2396,29 +2291,24 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.quiet[2]</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">burntOut.lead</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声がかかって、よかったです</t>
+          <t xml:space="preserve">その体は、とうに限界を過ぎていた。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.shy[1]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.body</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2428,29 +2318,24 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.shy[1]</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">burntOut.body</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+          <t xml:space="preserve">若い頃から追い込みを重ねた体だった。踏ん張りが効かず、崩れるように倒れた。請求書は、忘れた頃に届く。今日がその日だった。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.shy[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.title</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2460,29 +2345,24 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.shy[2]</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">lastWin.title</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+          <t xml:space="preserve">最 後 の 一 勝</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.easygoing[1]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.lead</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2492,29 +2372,24 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">lastWin.lead</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
+          <t xml:space="preserve">引退を表明していた。その最後の一勝だった。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.easygoing[2]</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.body</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2524,29 +2399,24 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.easygoing[2]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">lastWin.body</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声かかんなくてさー。拾ってくれて助かったよ</t>
+          <t xml:space="preserve">勝った直後に、彼女は動けなくなった。予定されていた引退試合は、もう組めない。花道は、その途中で終わった。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.earnest[1]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2556,29 +2426,24 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">mild[1]</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
+          <t xml:space="preserve">👁️ 業界筋が{name}の試合映像を取り寄せているらしい</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.earnest[2]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2588,29 +2453,24 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">mild[2]</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた恩は、練習の量でお返しします</t>
+          <t xml:space="preserve">👁️ {name}の名前が他団体の会議で挙がっていたとの噂</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.emotional[1]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[3]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2620,29 +2480,24 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">mild[3]</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
+          <t xml:space="preserve">👁️ {name}への注目度が他団体内で高まっているようだ</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES._default.emotional[2]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2652,29 +2507,24 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">_default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">moderate[1]</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた…！この恩、絶対に返す…！</t>
+          <t xml:space="preserve">👁️ {rival}のスカウトが{name}の試合をチェックしていた</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[1]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2684,24 +2534,24 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">moderate[2]</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
+          <t xml:space="preserve">👁️ {rival}関係者が{name}について詳しく探っているらしい</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[2]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[3]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2711,24 +2561,24 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">moderate[3]</t>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
+          <t xml:space="preserve">👁️ 業界紙が{name}を「動向注目の選手」として取り上げた</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_GENERIC_LINES[3]</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2738,24 +2588,24 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">serious[1]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
+          <t xml:space="preserve">⚠️ 複数の団体が{name}に接触を試みている噂が流れている</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].text</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2765,24 +2615,24 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].text</t>
+          <t xml:space="preserve">serious[2]</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🔥 苦しい中でもチームの結束が深まった</t>
+          <t xml:space="preserve">⚠️ {name}の周辺で他団体の動きが活発化している</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[1].detail</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[3]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -2792,24 +2642,24 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].detail</t>
+          <t xml:space="preserve">serious[3]</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">資金繰りは厳しいが、選手たちの表情に迷いはない。困難を共にすることで、絆が強まっているようだ。</t>
+          <t xml:space="preserve">⚠️ {name}への具体的なオファーが近いとの観測が出ている</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].text</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -2819,24 +2669,24 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].text</t>
+          <t xml:space="preserve">good[1]</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💪 逆境がチームを強くしている</t>
+          <t xml:space="preserve">💬 ロッカールームから笑い声が聞こえてくる</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[2].detail</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[2]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -2846,24 +2696,24 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].detail</t>
+          <t xml:space="preserve">good[2]</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">豪華な設備も潤沢な資金もない。だからこそ、選手同士で支え合う文化が自然に生まれている。</t>
+          <t xml:space="preserve">💬 控室の空気は和やかだ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].text</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[3]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -2873,24 +2723,24 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].text</t>
+          <t xml:space="preserve">good[3]</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🤝 厳しい時期だからこそ仲間の大切さを実感</t>
+          <t xml:space="preserve">💬 選手たちが自主練で残っている</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[3].detail</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[4]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -2900,24 +2750,24 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].detail</t>
+          <t xml:space="preserve">good[4]</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決して恵まれた環境ではない。それでも、誰一人として文句を言わずに練習に打ち込む姿がある。</t>
+          <t xml:space="preserve">💬 誰かが差し入れを持ってきたらしい</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].text</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -2927,24 +2777,24 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].text</t>
+          <t xml:space="preserve">warning[1]</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">✊ チーム全員が同じ方向を向いている</t>
+          <t xml:space="preserve">💬 控室で{name}がため息をついていた</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS[4].detail</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -2954,24 +2804,24 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].detail</t>
+          <t xml:space="preserve">warning[2]</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">苦しい状況を全員で分かち合っている。この経験が、いつかチームの財産になるはずだ。</t>
+          <t xml:space="preserve">💬 {name}の表情が最近硬い</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.title</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[3]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -2981,24 +2831,24 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pyrrhic.title</t>
+          <t xml:space="preserve">warning[3]</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝 者 の 代 償</t>
+          <t xml:space="preserve">💬 ロッカーの会話が少ない日が続いている</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.lead</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[4]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3008,24 +2858,24 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pyrrhic.lead</t>
+          <t xml:space="preserve">warning[4]</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その試合に、彼女は勝った。</t>
+          <t xml:space="preserve">💬 {name}が一人で帰る姿を見かけた</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.pyrrhic.body</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[5]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3035,24 +2885,24 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pyrrhic.body</t>
+          <t xml:space="preserve">warning[5]</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち名乗りを受けることは、なかった。担架が運び込まれ、歓声が戸惑いに変わっていく。後日、医師の所見が団体に届いた。もうリングには上がれない、と。</t>
+          <t xml:space="preserve">💬 練習後、{name}がスマホをじっと見つめていた</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.title</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3062,24 +2912,24 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.title</t>
+          <t xml:space="preserve">danger[1]</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王 座 を 守 っ て</t>
+          <t xml:space="preserve">💬 ロッカールームの空気が重い</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.lead</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[2]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3089,24 +2939,24 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.lead</t>
+          <t xml:space="preserve">danger[2]</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトは、守った。</t>
+          <t xml:space="preserve">💬 {name}と{name2}が何か話し込んでいた</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.defended.body</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[3]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3116,24 +2966,24 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.body</t>
+          <t xml:space="preserve">danger[3]</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛を告げるゴングの直後、王者はマットに崩れ落ちた。巻いたまま運ばれていく背中を、会場の誰もが見送るしかなかった。数日後、王座は返上されることになる。</t>
+          <t xml:space="preserve">💬 控室で小さな言い争いがあったらしい</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.title</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[4]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3143,24 +2993,24 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">neverCrowned.title</t>
+          <t xml:space="preserve">danger[4]</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">冠 に 届 か ず</t>
+          <t xml:space="preserve">💬 {name}の機嫌が明らかに悪い</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.lead</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[5]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3170,24 +3020,24 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">neverCrowned.lead</t>
+          <t xml:space="preserve">danger[5]</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一歩が、遠かった。</t>
+          <t xml:space="preserve">💬 誰もが口数少なく着替えを済ませていた</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.neverCrowned.body</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][1].text</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3197,24 +3047,24 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">neverCrowned.body</t>
+          <t xml:space="preserve">[1][1].text</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑戦は実らず、そしてそれが最後の試合になった。結局、彼女は一度もベルトを腰に巻かないまま去ることになる。記録に残るのは、挑戦者としての名前だけだ。</t>
+          <t xml:space="preserve">練習場が静まり返っている</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.title</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][2].text</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3224,24 +3074,24 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">burntOut.title</t>
+          <t xml:space="preserve">[1][2].text</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">追 い 込 み の ツ ケ</t>
+          <t xml:space="preserve">誰も目を合わせようとしない</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.lead</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][3].text</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3251,24 +3101,24 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">burntOut.lead</t>
+          <t xml:space="preserve">[1][3].text</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その体は、とうに限界を過ぎていた。</t>
+          <t xml:space="preserve">重い空気が漂っている</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.burntOut.body</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][1].text</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3278,24 +3128,24 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">burntOut.body</t>
+          <t xml:space="preserve">[2][1].text</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若い頃から追い込みを重ねた体だった。踏ん張りが効かず、崩れるように倒れた。請求書は、忘れた頃に届く。今日がその日だった。</t>
+          <t xml:space="preserve">どこかよそよそしい空気がある</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.title</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][2].text</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3305,24 +3155,24 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">lastWin.title</t>
+          <t xml:space="preserve">[2][2].text</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最 後 の 一 勝</t>
+          <t xml:space="preserve">最低限のメニューだけこなしている</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.lead</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][3].text</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3332,24 +3182,24 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">lastWin.lead</t>
+          <t xml:space="preserve">[2][3].text</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引退を表明していた。その最後の一勝だった。</t>
+          <t xml:space="preserve">会話が少ない</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT.lastWin.body</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][1].text</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3359,24 +3209,24 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">lastWin.body</t>
+          <t xml:space="preserve">[3][1].text</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った直後に、彼女は動けなくなった。予定されていた引退試合は、もう組めない。花道は、その途中で終わった。</t>
+          <t xml:space="preserve">淡々とメニューをこなしている</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[1]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][2].text</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3386,24 +3236,24 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mild[1]</t>
+          <t xml:space="preserve">[3][2].text</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ 業界筋が{name}の試合映像を取り寄せているらしい</t>
+          <t xml:space="preserve">いつも通りの練習風景</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[2]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][3].text</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3413,24 +3263,24 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mild[2]</t>
+          <t xml:space="preserve">[3][3].text</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {name}の名前が他団体の会議で挙がっていたとの噂</t>
+          <t xml:space="preserve">特に変わった様子はない</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.mild[3]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][4].text</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3440,24 +3290,24 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mild[3]</t>
+          <t xml:space="preserve">[3][4].text</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {name}への注目度が他団体内で高まっているようだ</t>
+          <t xml:space="preserve">黙々と汗を流している</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[1]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][1].text</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3467,24 +3317,24 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[1]</t>
+          <t xml:space="preserve">[4][1].text</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {rival}のスカウトが{name}の試合をチェックしていた</t>
+          <t xml:space="preserve">声が飛び交っている</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[2]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][2].text</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3494,24 +3344,24 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[2]</t>
+          <t xml:space="preserve">[4][2].text</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ {rival}関係者が{name}について詳しく探っているらしい</t>
+          <t xml:space="preserve">練習に熱が入っている</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.moderate[3]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][3].text</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3521,24 +3371,24 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">moderate[3]</t>
+          <t xml:space="preserve">[4][3].text</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👁️ 業界紙が{name}を「動向注目の選手」として取り上げた</t>
+          <t xml:space="preserve">選手同士でアドバイスし合っている</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[1]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][4].text</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3548,24 +3398,24 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">serious[1]</t>
+          <t xml:space="preserve">[4][4].text</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ 複数の団体が{name}に接触を試みている噂が流れている</t>
+          <t xml:space="preserve">活気のある練習場</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[2]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][1].text</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3575,24 +3425,24 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">serious[2]</t>
+          <t xml:space="preserve">[5][1].text</t>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}の周辺で他団体の動きが活発化している</t>
+          <t xml:space="preserve">自主練する選手が増えている</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS.serious[3]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][2].text</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -3602,24 +3452,24 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">serious[3]</t>
+          <t xml:space="preserve">[5][2].text</t>
         </is>
       </c>
       <c r="G120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}への具体的なオファーが近いとの観測が出ている</t>
+          <t xml:space="preserve">練習場に笑い声が響いている</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[1]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][3].text</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3629,24 +3479,24 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[1]</t>
+          <t xml:space="preserve">[5][3].text</t>
         </is>
       </c>
       <c r="G121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 ロッカールームから笑い声が聞こえてくる</t>
+          <t xml:space="preserve">全員の目つきが違う</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[2]</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][4].text</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3656,834 +3506,984 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[2]</t>
+          <t xml:space="preserve">[5][4].text</t>
         </is>
       </c>
       <c r="G122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 控室の空気は和やかだ</t>
+          <t xml:space="preserve">チーム全体に勢いがある</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[3]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.standard</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[3]</t>
+          <t xml:space="preserve">trust.standard</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 選手たちが自主練で残っている</t>
+          <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.good[4]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.ojousama</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">good[4]</t>
+          <t xml:space="preserve">trust.ojousama</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 誰かが差し入れを持ってきたらしい</t>
+          <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[1]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.delinquent</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[1]</t>
+          <t xml:space="preserve">trust.delinquent</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 控室で{name}がため息をついていた</t>
+          <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[2]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.cool</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[2]</t>
+          <t xml:space="preserve">trust.cool</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}の表情が最近硬い</t>
+          <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[3]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.seductive</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[3]</t>
+          <t xml:space="preserve">trust.seductive</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 ロッカーの会話が少ない日が続いている</t>
+          <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[4]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.polite</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[4]</t>
+          <t xml:space="preserve">trust.polite</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}が一人で帰る姿を見かけた</t>
+          <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.warning[5]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.composed</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warning[5]</t>
+          <t xml:space="preserve">trust.composed</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 練習後、{name}がスマホをじっと見つめていた</t>
+          <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[1]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.standard</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[1]</t>
+          <t xml:space="preserve">rival_friend.standard</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 ロッカールームの空気が重い</t>
+          <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[2]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.ojousama</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[2]</t>
+          <t xml:space="preserve">rival_friend.ojousama</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}と{name2}が何か話し込んでいた</t>
+          <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[3]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.delinquent</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[3]</t>
+          <t xml:space="preserve">rival_friend.delinquent</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 控室で小さな言い争いがあったらしい</t>
+          <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[4]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.cool</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[4]</t>
+          <t xml:space="preserve">rival_friend.cool</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 {name}の機嫌が明らかに悪い</t>
+          <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS.danger[5]</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.seductive</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">danger[5]</t>
+          <t xml:space="preserve">rival_friend.seductive</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💬 誰もが口数少なく着替えを済ませていた</t>
+          <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][1].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.polite</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1][1].text</t>
+          <t xml:space="preserve">rival_friend.polite</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場が静まり返っている</t>
+          <t xml:space="preserve">競い合えることが、自分の力になっています</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][2].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.composed</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1][2].text</t>
+          <t xml:space="preserve">rival_friend.composed</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰も目を合わせようとしない</t>
+          <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][3].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.standard</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1][3].text</t>
+          <t xml:space="preserve">destined_rival.standard</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重い空気が漂っている</t>
+          <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][1].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.ojousama</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][1].text</t>
+          <t xml:space="preserve">destined_rival.ojousama</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこかよそよそしい空気がある</t>
+          <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][2].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.delinquent</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][2].text</t>
+          <t xml:space="preserve">destined_rival.delinquent</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最低限のメニューだけこなしている</t>
+          <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][3].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.cool</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][3].text</t>
+          <t xml:space="preserve">destined_rival.cool</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">会話が少ない</t>
+          <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][1].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.seductive</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][1].text</t>
+          <t xml:space="preserve">destined_rival.seductive</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">淡々とメニューをこなしている</t>
+          <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][2].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.polite</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][2].text</t>
+          <t xml:space="preserve">destined_rival.polite</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りの練習風景</t>
+          <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][3].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.composed</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][3].text</t>
+          <t xml:space="preserve">destined_rival.composed</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特に変わった様子はない</t>
+          <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][4].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.standard</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][4].text</t>
+          <t xml:space="preserve">acquaintance.standard</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙々と汗を流している</t>
+          <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][1].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.ojousama</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][1].text</t>
+          <t xml:space="preserve">acquaintance.ojousama</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声が飛び交っている</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][2].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.delinquent</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][2].text</t>
+          <t xml:space="preserve">acquaintance.delinquent</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習に熱が入っている</t>
+          <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][3].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.cool</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][3].text</t>
+          <t xml:space="preserve">acquaintance.cool</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手同士でアドバイスし合っている</t>
+          <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][4].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.seductive</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][4].text</t>
+          <t xml:space="preserve">acquaintance.seductive</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活気のある練習場</t>
+          <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][1].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.polite</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][1].text</t>
+          <t xml:space="preserve">acquaintance.polite</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自主練する選手が増えている</t>
+          <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][2].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.composed</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][2].text</t>
+          <t xml:space="preserve">acquaintance.composed</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場に笑い声が響いている</t>
+          <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][3].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.standard</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][3].text</t>
+          <t xml:space="preserve">intrigued.standard</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員の目つきが違う</t>
+          <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][4].text</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.ojousama</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][4].text</t>
+          <t xml:space="preserve">intrigued.ojousama</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チーム全体に勢いがある</t>
+          <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.delinquent</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4498,24 +4498,24 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.standard</t>
+          <t xml:space="preserve">intrigued.delinquent</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
+          <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.cool</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4530,24 +4530,24 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.ojousama</t>
+          <t xml:space="preserve">intrigued.cool</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
+          <t xml:space="preserve">気にしていないつもりだった……</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.seductive</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -4562,24 +4562,24 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.delinquent</t>
+          <t xml:space="preserve">intrigued.seductive</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
+          <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.polite</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -4594,24 +4594,24 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.cool</t>
+          <t xml:space="preserve">intrigued.polite</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
+          <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.composed</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.seductive</t>
+          <t xml:space="preserve">intrigued.composed</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
+          <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.standard</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -4658,24 +4658,24 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.polite</t>
+          <t xml:space="preserve">hostile_competitor.standard</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
+          <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.ojousama</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -4690,24 +4690,24 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.composed</t>
+          <t xml:space="preserve">hostile_competitor.ojousama</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
+          <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.delinquent</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -4722,24 +4722,24 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.standard</t>
+          <t xml:space="preserve">hostile_competitor.delinquent</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
+          <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.cool</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -4754,24 +4754,24 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.ojousama</t>
+          <t xml:space="preserve">hostile_competitor.cool</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
+          <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.seductive</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -4786,24 +4786,24 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.delinquent</t>
+          <t xml:space="preserve">hostile_competitor.seductive</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
+          <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.polite</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -4818,24 +4818,24 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.cool</t>
+          <t xml:space="preserve">hostile_competitor.polite</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
+          <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.composed</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -4850,24 +4850,24 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.seductive</t>
+          <t xml:space="preserve">hostile_competitor.composed</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
+          <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.standard</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -4882,24 +4882,24 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.polite</t>
+          <t xml:space="preserve">distant.standard</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">競い合えることが、自分の力になっています</t>
+          <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.ojousama</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -4914,24 +4914,24 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.composed</t>
+          <t xml:space="preserve">distant.ojousama</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.delinquent</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -4946,24 +4946,24 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.standard</t>
+          <t xml:space="preserve">distant.delinquent</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
+          <t xml:space="preserve">あー、いたな。それで?</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.cool</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -4978,24 +4978,24 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.ojousama</t>
+          <t xml:space="preserve">distant.cool</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
+          <t xml:space="preserve">認識しているだけ。それ以上はない</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.seductive</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5010,24 +5010,24 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.delinquent</t>
+          <t xml:space="preserve">distant.seductive</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.polite</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5042,24 +5042,24 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.cool</t>
+          <t xml:space="preserve">distant.polite</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
+          <t xml:space="preserve">お見かけはしますけれど、特には……</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.composed</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5074,24 +5074,24 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.seductive</t>
+          <t xml:space="preserve">distant.composed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
+          <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.standard</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5106,24 +5106,24 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.polite</t>
+          <t xml:space="preserve">contempt.standard</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
+          <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.ojousama</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5138,24 +5138,24 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.composed</t>
+          <t xml:space="preserve">contempt.ojousama</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
+          <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.delinquent</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5170,24 +5170,24 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.standard</t>
+          <t xml:space="preserve">contempt.delinquent</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
+          <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.cool</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5202,24 +5202,24 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.ojousama</t>
+          <t xml:space="preserve">contempt.cool</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
+          <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.seductive</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5234,24 +5234,24 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.delinquent</t>
+          <t xml:space="preserve">contempt.seductive</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
+          <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.polite</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.cool</t>
+          <t xml:space="preserve">contempt.polite</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
+          <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.composed</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5298,24 +5298,24 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.seductive</t>
+          <t xml:space="preserve">contempt.composed</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
+          <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.standard</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5330,24 +5330,24 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.polite</t>
+          <t xml:space="preserve">irritation.standard</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
+          <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.ojousama</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5362,24 +5362,24 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.composed</t>
+          <t xml:space="preserve">irritation.ojousama</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
+          <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.delinquent</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5394,24 +5394,24 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.standard</t>
+          <t xml:space="preserve">irritation.delinquent</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
+          <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.cool</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5426,24 +5426,24 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.ojousama</t>
+          <t xml:space="preserve">irritation.cool</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
+          <t xml:space="preserve">不快。距離を取りたい</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.seductive</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -5458,24 +5458,24 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.delinquent</t>
+          <t xml:space="preserve">irritation.seductive</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
+          <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.polite</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5490,24 +5490,24 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.cool</t>
+          <t xml:space="preserve">irritation.polite</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気にしていないつもりだった……</t>
+          <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.composed</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5522,24 +5522,24 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.seductive</t>
+          <t xml:space="preserve">irritation.composed</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
+          <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.standard</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5554,24 +5554,24 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.polite</t>
+          <t xml:space="preserve">dislike.standard</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
+          <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.ojousama</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -5586,24 +5586,24 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.composed</t>
+          <t xml:space="preserve">dislike.ojousama</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
+          <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.delinquent</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -5618,24 +5618,24 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.standard</t>
+          <t xml:space="preserve">dislike.delinquent</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
+          <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.cool</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -5650,24 +5650,24 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.ojousama</t>
+          <t xml:space="preserve">dislike.cool</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
+          <t xml:space="preserve">受け付けない。理屈じゃない</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.seductive</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -5682,24 +5682,24 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.delinquent</t>
+          <t xml:space="preserve">dislike.seductive</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
+          <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.polite</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -5714,24 +5714,24 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.cool</t>
+          <t xml:space="preserve">dislike.polite</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
+          <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.composed</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.seductive</t>
+          <t xml:space="preserve">dislike.composed</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
+          <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.standard</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -5778,24 +5778,24 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.polite</t>
+          <t xml:space="preserve">cold_loathing.standard</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
+          <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.ojousama</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -5810,24 +5810,24 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.composed</t>
+          <t xml:space="preserve">cold_loathing.ojousama</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
+          <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.delinquent</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -5842,24 +5842,24 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.standard</t>
+          <t xml:space="preserve">cold_loathing.delinquent</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
+          <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.cool</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -5874,24 +5874,24 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.ojousama</t>
+          <t xml:space="preserve">cold_loathing.cool</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
+          <t xml:space="preserve">存在を認識から外している。話すこともない</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.seductive</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -5906,24 +5906,24 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.delinquent</t>
+          <t xml:space="preserve">cold_loathing.seductive</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いたな。それで?</t>
+          <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.polite</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -5938,24 +5938,24 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.cool</t>
+          <t xml:space="preserve">cold_loathing.polite</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認識しているだけ。それ以上はない</t>
+          <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.composed</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -5970,24 +5970,24 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.seductive</t>
+          <t xml:space="preserve">cold_loathing.composed</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
+          <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.standard</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6002,24 +6002,24 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.polite</t>
+          <t xml:space="preserve">dislike_strong.standard</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますけれど、特には……</t>
+          <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.ojousama</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6034,24 +6034,24 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.composed</t>
+          <t xml:space="preserve">dislike_strong.ojousama</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
+          <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.delinquent</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6066,24 +6066,24 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.standard</t>
+          <t xml:space="preserve">dislike_strong.delinquent</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
+          <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.cool</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6098,24 +6098,24 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.ojousama</t>
+          <t xml:space="preserve">dislike_strong.cool</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
+          <t xml:space="preserve">生理的に駄目。これは変わらない</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.seductive</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.delinquent</t>
+          <t xml:space="preserve">dislike_strong.seductive</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
+          <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.polite</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6162,24 +6162,24 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.cool</t>
+          <t xml:space="preserve">dislike_strong.polite</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
+          <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.composed</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6194,24 +6194,24 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.seductive</t>
+          <t xml:space="preserve">dislike_strong.composed</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
+          <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.standard</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6226,24 +6226,24 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.polite</t>
+          <t xml:space="preserve">hatred.standard</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
+          <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.ojousama</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6258,24 +6258,24 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.composed</t>
+          <t xml:space="preserve">hatred.ojousama</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
+          <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.delinquent</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6290,24 +6290,24 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.standard</t>
+          <t xml:space="preserve">hatred.delinquent</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
+          <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.cool</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6322,24 +6322,24 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.ojousama</t>
+          <t xml:space="preserve">hatred.cool</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
+          <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.seductive</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6354,24 +6354,24 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.delinquent</t>
+          <t xml:space="preserve">hatred.seductive</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
+          <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.polite</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6386,24 +6386,24 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.cool</t>
+          <t xml:space="preserve">hatred.polite</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不快。距離を取りたい</t>
+          <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.composed</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6418,1252 +6418,292 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.seductive</t>
+          <t xml:space="preserve">hatred.composed</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
+          <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.polite</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[1].label</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.polite</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[1].label</t>
         </is>
       </c>
       <c r="G214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
+          <t xml:space="preserve">初興行収入</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.composed</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[1].desc</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.composed</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[1].desc</t>
         </is>
       </c>
       <c r="G215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
+          <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.standard</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[2].label</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.standard</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">[2].label</t>
         </is>
       </c>
       <c r="G216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
+          <t xml:space="preserve">スポンサー獲得</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.ojousama</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[2].desc</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.ojousama</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">[2].desc</t>
         </is>
       </c>
       <c r="G217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
+          <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.delinquent</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[3].label</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.delinquent</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">[3].label</t>
         </is>
       </c>
       <c r="G218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
+          <t xml:space="preserve">初の月次黒字</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.cool</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[3].desc</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.cool</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">[3].desc</t>
         </is>
       </c>
       <c r="G219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受け付けない。理屈じゃない</t>
+          <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.seductive</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[4].label</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.seductive</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">[4].label</t>
         </is>
       </c>
       <c r="G220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
+          <t xml:space="preserve">2ヶ月連続月次黒字</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.polite</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[4].desc</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.polite</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[4].desc</t>
         </is>
       </c>
       <c r="G221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
+          <t xml:space="preserve">安定経営が見えてきた</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.composed</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[5].label</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.composed</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[5].label</t>
         </is>
       </c>
       <c r="G222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
+          <t xml:space="preserve">経営安定化</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.standard</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[5].desc</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.standard</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">[5].desc</t>
         </is>
       </c>
       <c r="G223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="40" customHeight="1">
-      <c r="A224" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.ojousama</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cold_loathing.ojousama</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="40" customHeight="1">
-      <c r="A225" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.delinquent</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cold_loathing.delinquent</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="40" customHeight="1">
-      <c r="A226" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.cool</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cold_loathing.cool</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">存在を認識から外している。話すこともない</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="40" customHeight="1">
-      <c r="A227" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.seductive</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cold_loathing.seductive</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="40" customHeight="1">
-      <c r="A228" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.polite</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cold_loathing.polite</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="40" customHeight="1">
-      <c r="A229" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.composed</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cold_loathing.composed</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="40" customHeight="1">
-      <c r="A230" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.standard</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.standard</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="40" customHeight="1">
-      <c r="A231" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.ojousama</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.ojousama</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="40" customHeight="1">
-      <c r="A232" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.delinquent</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.delinquent</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="40" customHeight="1">
-      <c r="A233" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.cool</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.cool</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">生理的に駄目。これは変わらない</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="40" customHeight="1">
-      <c r="A234" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.seductive</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.seductive</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="40" customHeight="1">
-      <c r="A235" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.polite</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.polite</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="40" customHeight="1">
-      <c r="A236" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.composed</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">dislike_strong.composed</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="40" customHeight="1">
-      <c r="A237" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.standard</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.standard</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="40" customHeight="1">
-      <c r="A238" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.ojousama</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.ojousama</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="40" customHeight="1">
-      <c r="A239" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.delinquent</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.delinquent</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="40" customHeight="1">
-      <c r="A240" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.cool</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.cool</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="40" customHeight="1">
-      <c r="A241" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.seductive</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.seductive</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="40" customHeight="1">
-      <c r="A242" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.polite</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.polite</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="40" customHeight="1">
-      <c r="A243" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.composed</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/ui-render.js</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">hatred.composed</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="40" customHeight="1">
-      <c r="A244" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[1].label</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[1].label</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">初興行収入</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="40" customHeight="1">
-      <c r="A245" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[1].desc</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[1].desc</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="40" customHeight="1">
-      <c r="A246" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[2].label</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[2].label</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">スポンサー獲得</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="40" customHeight="1">
-      <c r="A247" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[2].desc</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[2].desc</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="40" customHeight="1">
-      <c r="A248" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[3].label</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[3].label</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">初の月次黒字</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="40" customHeight="1">
-      <c r="A249" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[3].desc</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[3].desc</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="40" customHeight="1">
-      <c r="A250" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[4].label</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[4].label</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2ヶ月連続月次黒字</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="40" customHeight="1">
-      <c r="A251" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[4].desc</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[4].desc</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">安定経営が見えてきた</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="40" customHeight="1">
-      <c r="A252" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[5].label</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[5].label</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">経営安定化</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="40" customHeight="1">
-      <c r="A253" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[5].desc</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/app.js</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">[5].desc</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">月次黒字定着＋資金確保！サバイバルクリア</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I253"/>
+  <autoFilter ref="A1:I223"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
+++ b/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
@@ -192,18 +192,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:J223"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -214,40 +215,45 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">カテゴリ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">出典</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">テーブル</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">パス</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">archetype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">personality</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">現在</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">改訂</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">備考</t>
         </is>
@@ -261,20 +267,25 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="12">
+      <c r="E2" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_s[1]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr" s="3">
+      <c r="H2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、引く気配なし</t>
         </is>
@@ -288,20 +299,25 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr" s="12">
+      <c r="E3" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_s[2]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr" s="3">
+      <c r="H3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、王者の貫禄で粘る</t>
         </is>
@@ -315,20 +331,25 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="D4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="12">
+      <c r="E4" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_s[3]</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr" s="3">
+      <c r="H4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、余裕の表情を崩さない</t>
         </is>
@@ -342,20 +363,25 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
+      <c r="D5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="12">
+      <c r="E5" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_s[4]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr" s="3">
+      <c r="H5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、資金力を背景にじわじわ圧をかける</t>
         </is>
@@ -369,20 +395,25 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="D6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="12">
+      <c r="E6" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_a[1]</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr" s="3">
+      <c r="H6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、ヒートアップ</t>
         </is>
@@ -396,20 +427,25 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="D7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="12">
+      <c r="E7" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_a[2]</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr" s="3">
+      <c r="H7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、勝負に出た</t>
         </is>
@@ -423,20 +459,25 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="2">
+      <c r="D8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="12">
+      <c r="E8" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_a[3]</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr" s="3">
+      <c r="H8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、若い情熱で食い下がる</t>
         </is>
@@ -450,20 +491,25 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="2">
+      <c r="D9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="12">
+      <c r="E9" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_a[4]</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr" s="3">
+      <c r="H9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、ここで引いたら育成計画が崩れる</t>
         </is>
@@ -477,20 +523,25 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="2">
+      <c r="D10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="12">
+      <c r="E10" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_b[1]</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr" s="3">
+      <c r="H10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、まさかの執念</t>
         </is>
@@ -504,20 +555,25 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="2">
+      <c r="D11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="12">
+      <c r="E11" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_b[2]</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr" s="3">
+      <c r="H11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、地方の意地を見せる</t>
         </is>
@@ -531,20 +587,25 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="2">
+      <c r="D12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr" s="12">
+      <c r="E12" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_b[3]</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr" s="3">
+      <c r="H12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、小さな団体の大きな賭け</t>
         </is>
@@ -558,20 +619,25 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
+      <c r="D13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr" s="12">
+      <c r="E13" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighting.org_b[4]</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr" s="3">
+      <c r="H13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、身の丈を超えた挑戦</t>
         </is>
@@ -585,20 +651,25 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="2">
+      <c r="D14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="12">
+      <c r="E14" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_s[1]</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr" s="3">
+      <c r="H14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、ここで撤退。王者にも見切り時はある</t>
         </is>
@@ -612,20 +683,25 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="2">
+      <c r="D15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr" s="12">
+      <c r="E15" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_s[2]</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr" s="3">
+      <c r="H15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、苦渋の判断で離脱。次の獲物を見据えるか</t>
         </is>
@@ -639,20 +715,25 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="2">
+      <c r="D16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr" s="12">
+      <c r="E16" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_s[3]</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr" s="3">
+      <c r="H16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、静かに席を立った。その背中に敗北の影はない</t>
         </is>
@@ -666,20 +747,25 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="2">
+      <c r="D17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr" s="12">
+      <c r="E17" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_a[1]</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr" s="3">
+      <c r="H17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、無念の撤退</t>
         </is>
@@ -693,20 +779,25 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr" s="2">
+      <c r="D18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr" s="12">
+      <c r="E18" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_a[2]</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr" s="3">
+      <c r="H18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、ここは引くしかなかった。拳を握りしめている</t>
         </is>
@@ -720,20 +811,25 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr" s="2">
+      <c r="D19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="12">
+      <c r="E19" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_a[3]</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr" s="3">
+      <c r="H19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、予算の限界。悔しさを滲ませて離脱</t>
         </is>
@@ -747,20 +843,25 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr" s="2">
+      <c r="D20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr" s="12">
+      <c r="E20" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_b[1]</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr" s="3">
+      <c r="H20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、現実的な判断で離脱</t>
         </is>
@@ -774,20 +875,25 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr" s="2">
+      <c r="D21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr" s="12">
+      <c r="E21" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_b[2]</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr" s="3">
+      <c r="H21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、深追いせず撤退。堅実経営の信条を貫く</t>
         </is>
@@ -801,20 +907,25 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr" s="2">
+      <c r="D22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr" s="12">
+      <c r="E22" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dropped.org_b[3]</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr" s="3">
+      <c r="H22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{ORG}、これ以上は無理と判断。潔い引き際</t>
         </is>
@@ -828,20 +939,25 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr" s="2">
+      <c r="D23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr" s="12">
+      <c r="E23" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.solo[1]</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr" s="3">
+      <c r="H23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">契約成立。静かに迎え入れる</t>
         </is>
@@ -855,20 +971,25 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr" s="2">
+      <c r="D24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr" s="12">
+      <c r="E24" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.solo[2]</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr" s="3">
+      <c r="H24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">他に名乗りを上げる者はなかった。交渉成立</t>
         </is>
@@ -882,20 +1003,25 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr" s="2">
+      <c r="D25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="12">
+      <c r="E25" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.vs1[1]</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr" s="3">
+      <c r="H25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">一騎打ちを制した</t>
         </is>
@@ -909,20 +1035,25 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr" s="2">
+      <c r="D26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="12">
+      <c r="E26" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.vs1[2]</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr" s="3">
+      <c r="H26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">激しい交渉を勝ち抜いた</t>
         </is>
@@ -936,20 +1067,25 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr" s="2">
+      <c r="D27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr" s="12">
+      <c r="E27" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.vs1[3]</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr" s="3">
+      <c r="H27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">粘り強い交渉が実を結んだ</t>
         </is>
@@ -963,20 +1099,25 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr" s="2">
+      <c r="D28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr" s="12">
+      <c r="E28" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.multi[1]</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr" s="3">
+      <c r="H28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">複数団体との争奪戦を勝ち抜いた！</t>
         </is>
@@ -990,20 +1131,25 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr" s="2">
+      <c r="D29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="12">
+      <c r="E29" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.multi[2]</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr" s="3">
+      <c r="H29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">激戦の末、獲得に成功！</t>
         </is>
@@ -1017,20 +1163,25 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr" s="2">
+      <c r="D30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="12">
+      <c r="E30" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerWin.multi[3]</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr" s="3">
+      <c r="H30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">3団体を退けての獲得。この選手にかけた執念が勝った</t>
         </is>
@@ -1044,20 +1195,25 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr" s="2">
+      <c r="D31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="12">
+      <c r="E31" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerLost[1]</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr" s="3">
+      <c r="H31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">他団体に持っていかれた。次の機会を待とう</t>
         </is>
@@ -1071,20 +1227,25 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr" s="2">
+      <c r="D32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr" s="12">
+      <c r="E32" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerLost[2]</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr" s="3">
+      <c r="H32" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">残念…他団体の執念が上回った</t>
         </is>
@@ -1098,20 +1259,25 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr" s="2">
+      <c r="D33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="12">
+      <c r="E33" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">playerLost[3]</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr" s="3">
+      <c r="H33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">相手の本気度が一枚上手だった。縁がなかったと割り切るしかない</t>
         </is>
@@ -1125,20 +1291,25 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr" s="2">
+      <c r="D34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr" s="12">
+      <c r="E34" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">flowThrough[1]</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr" s="3">
+      <c r="H34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">全団体が手を引いた。この選手はフリー市場へ</t>
         </is>
@@ -1152,20 +1323,25 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr" s="2">
+      <c r="D35" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="12">
+      <c r="E35" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">flowThrough[2]</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr" s="3">
+      <c r="H35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">誰も最後まで残らなかった。フリーエージェントとして再出発</t>
         </is>
@@ -1179,20 +1355,25 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="2">
+      <c r="D36" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr" s="12">
+      <c r="E36" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">roundStart[1]</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr" s="3">
+      <c r="H36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">交渉卓に緊張が走る</t>
         </is>
@@ -1206,20 +1387,25 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="2">
+      <c r="D37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="12">
+      <c r="E37" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">roundStart[2]</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr" s="3">
+      <c r="H37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">各団体の代表が表情を引き締める</t>
         </is>
@@ -1233,20 +1419,25 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr" s="2">
+      <c r="D38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr" s="12">
+      <c r="E38" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">roundStart[3]</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr" s="3">
+      <c r="H38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">金額が上がるごとに空気が重くなる</t>
         </is>
@@ -1260,20 +1451,25 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="2">
+      <c r="D39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="12">
+      <c r="E39" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">roundStart[4]</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr" s="3">
+      <c r="H39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">交渉は佳境を迎えている</t>
         </is>
@@ -1287,20 +1483,25 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr" s="2">
+      <c r="D40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr" s="12">
+      <c r="E40" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">roundStart[5]</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr" s="3">
+      <c r="H40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">静かな駆け引きが続く</t>
         </is>
@@ -1314,20 +1515,25 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/draft-negotiation.js</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr" s="2">
+      <c r="D41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draftNegotiation.NARRATION</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="12">
+      <c r="E41" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">roundStart[6]</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr" s="3">
+      <c r="H41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">次の一手が勝敗を分ける</t>
         </is>
@@ -1341,20 +1547,25 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr" s="2">
+      <c r="D42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.scout.TIERS</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="12">
+      <c r="E42" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1].label</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr" s="3">
+      <c r="H42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">超逸材</t>
         </is>
@@ -1368,20 +1579,25 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr" s="2">
+      <c r="D43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.scout.TIERS</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="12">
+      <c r="E43" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2].label</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr" s="3">
+      <c r="H43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">逸材</t>
         </is>
@@ -1395,20 +1611,25 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr" s="2">
+      <c r="D44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.scout.TIERS</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr" s="12">
+      <c r="E44" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3].label</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr" s="3">
+      <c r="H44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">有望</t>
         </is>
@@ -1422,20 +1643,25 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr" s="2">
+      <c r="D45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.scout.TIERS</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="12">
+      <c r="E45" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4].label</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr" s="3">
+      <c r="H45" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">原石</t>
         </is>
@@ -1449,20 +1675,25 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr" s="2">
+      <c r="D46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.scout.TIERS</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr" s="12">
+      <c r="E46" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5].label</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr" s="3">
+      <c r="H46" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">素材</t>
         </is>
@@ -1476,20 +1707,25 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr" s="2">
+      <c r="D47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draft.EVAL_TIERS</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr" s="12">
+      <c r="E47" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1].text</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr" s="3">
+      <c r="H47" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">将来のエース候補</t>
         </is>
@@ -1503,20 +1739,25 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr" s="2">
+      <c r="D48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draft.EVAL_TIERS</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr" s="12">
+      <c r="E48" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2].text</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr" s="3">
+      <c r="H48" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">逸材の匂いがする</t>
         </is>
@@ -1530,20 +1771,25 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr" s="2">
+      <c r="D49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draft.EVAL_TIERS</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr" s="12">
+      <c r="E49" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3].text</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr" s="3">
+      <c r="H49" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">かなりの素質あり</t>
         </is>
@@ -1557,20 +1803,25 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr" s="2">
+      <c r="D50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draft.EVAL_TIERS</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr" s="12">
+      <c r="E50" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4].text</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr" s="3">
+      <c r="H50" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">十分な伸びしろ</t>
         </is>
@@ -1584,20 +1835,25 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr" s="2">
+      <c r="D51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draft.EVAL_TIERS</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr" s="12">
+      <c r="E51" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5].text</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr" s="3">
+      <c r="H51" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">堅実に育つタイプ</t>
         </is>
@@ -1611,20 +1867,25 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/management.js</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr" s="2">
+      <c r="D52" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Engine.draft.EVAL_TIERS</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr" s="12">
+      <c r="E52" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6].text</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr" s="3">
+      <c r="H52" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">未知数</t>
         </is>
@@ -1638,20 +1899,25 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr" s="2">
+      <c r="D53" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr" s="12">
+      <c r="E53" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr" s="3">
+      <c r="H53" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
         </is>
@@ -1665,20 +1931,25 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr" s="2">
+      <c r="D54" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr" s="12">
+      <c r="E54" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr" s="3">
+      <c r="H54" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
         </is>
@@ -1692,20 +1963,25 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr" s="2">
+      <c r="D55" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_GENERIC_LINES</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr" s="12">
+      <c r="E55" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr" s="3">
+      <c r="H55" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
         </is>
@@ -1719,20 +1995,25 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr" s="2">
+      <c r="D56" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr" s="12">
+      <c r="E56" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr" s="3">
+      <c r="H56" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
         </is>
@@ -1746,20 +2027,25 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr" s="2">
+      <c r="D57" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr" s="12">
+      <c r="E57" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr" s="3">
+      <c r="H57" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
         </is>
@@ -1773,20 +2059,25 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr" s="2">
+      <c r="D58" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FA_GREETING_GENERIC_LINES</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr" s="12">
+      <c r="E58" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr" s="3">
+      <c r="H58" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
         </is>
@@ -1800,20 +2091,25 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr" s="2">
+      <c r="D59" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr" s="12">
+      <c r="E59" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1].text</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr" s="3">
+      <c r="H59" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🔥 苦しい中でもチームの結束が深まった</t>
         </is>
@@ -1827,20 +2123,25 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr" s="2">
+      <c r="D60" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr" s="12">
+      <c r="E60" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1].detail</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr" s="3">
+      <c r="H60" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">資金繰りは厳しいが、選手たちの表情に迷いはない。困難を共にすることで、絆が強まっているようだ。</t>
         </is>
@@ -1854,20 +2155,25 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr" s="2">
+      <c r="D61" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr" s="12">
+      <c r="E61" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2].text</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr" s="3">
+      <c r="H61" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💪 逆境がチームを強くしている</t>
         </is>
@@ -1881,20 +2187,25 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr" s="2">
+      <c r="D62" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr" s="12">
+      <c r="E62" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2].detail</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr" s="3">
+      <c r="H62" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">豪華な設備も潤沢な資金もない。だからこそ、選手同士で支え合う文化が自然に生まれている。</t>
         </is>
@@ -1908,20 +2219,25 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr" s="2">
+      <c r="D63" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr" s="12">
+      <c r="E63" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3].text</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr" s="3">
+      <c r="H63" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤝 厳しい時期だからこそ仲間の大切さを実感</t>
         </is>
@@ -1935,20 +2251,25 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr" s="2">
+      <c r="D64" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr" s="12">
+      <c r="E64" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3].detail</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr" s="3">
+      <c r="H64" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">決して恵まれた環境ではない。それでも、誰一人として文句を言わずに練習に打ち込む姿がある。</t>
         </is>
@@ -1962,20 +2283,25 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr" s="2">
+      <c r="D65" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr" s="12">
+      <c r="E65" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4].text</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr" s="3">
+      <c r="H65" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">✊ チーム全員が同じ方向を向いている</t>
         </is>
@@ -1989,20 +2315,25 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr" s="2">
+      <c r="D66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">TEAM_SPIRIT_TEXTS</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr" s="12">
+      <c r="E66" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4].detail</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr" s="3">
+      <c r="H66" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">苦しい状況を全員で分かち合っている。この経験が、いつかチームの財産になるはずだ。</t>
         </is>
@@ -2016,20 +2347,25 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr" s="2">
+      <c r="D67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr" s="12">
+      <c r="E67" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">pyrrhic.title</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr" s="3">
+      <c r="H67" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">勝 者 の 代 償</t>
         </is>
@@ -2043,20 +2379,25 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr" s="2">
+      <c r="D68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr" s="12">
+      <c r="E68" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">pyrrhic.lead</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr" s="3">
+      <c r="H68" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">その試合に、彼女は勝った。</t>
         </is>
@@ -2070,20 +2411,25 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr" s="2">
+      <c r="D69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr" s="12">
+      <c r="E69" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">pyrrhic.body</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr" s="3">
+      <c r="H69" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">勝ち名乗りを受けることは、なかった。担架が運び込まれ、歓声が戸惑いに変わっていく。後日、医師の所見が団体に届いた。もうリングには上がれない、と。</t>
         </is>
@@ -2097,20 +2443,25 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr" s="2">
+      <c r="D70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr" s="12">
+      <c r="E70" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">defended.title</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr" s="3">
+      <c r="H70" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">王 座 を 守 っ て</t>
         </is>
@@ -2124,20 +2475,25 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr" s="2">
+      <c r="D71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr" s="12">
+      <c r="E71" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">defended.lead</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr" s="3">
+      <c r="H71" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ベルトは、守った。</t>
         </is>
@@ -2151,20 +2507,25 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr" s="2">
+      <c r="D72" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr" s="12">
+      <c r="E72" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">defended.body</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr" s="3">
+      <c r="H72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">防衛を告げるゴングの直後、王者はマットに崩れ落ちた。巻いたまま運ばれていく背中を、会場の誰もが見送るしかなかった。数日後、王座は返上されることになる。</t>
         </is>
@@ -2178,20 +2539,25 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr" s="2">
+      <c r="D73" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr" s="12">
+      <c r="E73" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">neverCrowned.title</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr" s="3">
+      <c r="H73" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">冠 に 届 か ず</t>
         </is>
@@ -2205,20 +2571,25 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr" s="2">
+      <c r="D74" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr" s="12">
+      <c r="E74" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">neverCrowned.lead</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr" s="3">
+      <c r="H74" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あと一歩が、遠かった。</t>
         </is>
@@ -2232,20 +2603,25 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr" s="2">
+      <c r="D75" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr" s="12">
+      <c r="E75" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">neverCrowned.body</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr" s="3">
+      <c r="H75" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">挑戦は実らず、そしてそれが最後の試合になった。結局、彼女は一度もベルトを腰に巻かないまま去ることになる。記録に残るのは、挑戦者としての名前だけだ。</t>
         </is>
@@ -2259,20 +2635,25 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr" s="2">
+      <c r="D76" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr" s="12">
+      <c r="E76" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">burntOut.title</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr" s="3">
+      <c r="H76" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">追 い 込 み の ツ ケ</t>
         </is>
@@ -2286,20 +2667,25 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr" s="2">
+      <c r="D77" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr" s="12">
+      <c r="E77" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">burntOut.lead</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr" s="3">
+      <c r="H77" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">その体は、とうに限界を過ぎていた。</t>
         </is>
@@ -2313,20 +2699,25 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr" s="2">
+      <c r="D78" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr" s="12">
+      <c r="E78" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">burntOut.body</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr" s="3">
+      <c r="H78" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">若い頃から追い込みを重ねた体だった。踏ん張りが効かず、崩れるように倒れた。請求書は、忘れた頃に届く。今日がその日だった。</t>
         </is>
@@ -2340,20 +2731,25 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr" s="2">
+      <c r="D79" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr" s="12">
+      <c r="E79" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">lastWin.title</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr" s="3">
+      <c r="H79" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最 後 の 一 勝</t>
         </is>
@@ -2367,20 +2763,25 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr" s="2">
+      <c r="D80" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr" s="12">
+      <c r="E80" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">lastWin.lead</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr" s="3">
+      <c r="H80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">引退を表明していた。その最後の一勝だった。</t>
         </is>
@@ -2394,20 +2795,25 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr" s="2">
+      <c r="D81" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FAREWELL_KIND_TEXT</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr" s="12">
+      <c r="E81" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">lastWin.body</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr" s="3">
+      <c r="H81" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">勝った直後に、彼女は動けなくなった。予定されていた引退試合は、もう組めない。花道は、その途中で終わった。</t>
         </is>
@@ -2421,20 +2827,25 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr" s="2">
+      <c r="D82" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr" s="12">
+      <c r="E82" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">mild[1]</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr" s="3">
+      <c r="H82" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👁️ 業界筋が{name}の試合映像を取り寄せているらしい</t>
         </is>
@@ -2448,20 +2859,25 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr" s="2">
+      <c r="D83" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr" s="12">
+      <c r="E83" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">mild[2]</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr" s="3">
+      <c r="H83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👁️ {name}の名前が他団体の会議で挙がっていたとの噂</t>
         </is>
@@ -2475,20 +2891,25 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr" s="2">
+      <c r="D84" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr" s="12">
+      <c r="E84" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">mild[3]</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr" s="3">
+      <c r="H84" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👁️ {name}への注目度が他団体内で高まっているようだ</t>
         </is>
@@ -2502,20 +2923,25 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr" s="2">
+      <c r="D85" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr" s="12">
+      <c r="E85" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">moderate[1]</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr" s="3">
+      <c r="H85" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👁️ {rival}のスカウトが{name}の試合をチェックしていた</t>
         </is>
@@ -2529,20 +2955,25 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr" s="2">
+      <c r="D86" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr" s="12">
+      <c r="E86" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">moderate[2]</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr" s="3">
+      <c r="H86" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👁️ {rival}関係者が{name}について詳しく探っているらしい</t>
         </is>
@@ -2556,20 +2987,25 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr" s="2">
+      <c r="D87" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr" s="12">
+      <c r="E87" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">moderate[3]</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr" s="3">
+      <c r="H87" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👁️ 業界紙が{name}を「動向注目の選手」として取り上げた</t>
         </is>
@@ -2583,20 +3019,25 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="2">
+      <c r="D88" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr" s="12">
+      <c r="E88" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">serious[1]</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr" s="3">
+      <c r="H88" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ 複数の団体が{name}に接触を試みている噂が流れている</t>
         </is>
@@ -2610,20 +3051,25 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr" s="2">
+      <c r="D89" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr" s="12">
+      <c r="E89" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">serious[2]</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr" s="3">
+      <c r="H89" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}の周辺で他団体の動きが活発化している</t>
         </is>
@@ -2637,20 +3083,25 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr" s="2">
+      <c r="D90" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">PRE_WINDOW_TEXTS</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr" s="12">
+      <c r="E90" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">serious[3]</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr" s="3">
+      <c r="H90" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}への具体的なオファーが近いとの観測が出ている</t>
         </is>
@@ -2664,20 +3115,25 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr" s="2">
+      <c r="D91" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr" s="12">
+      <c r="E91" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">good[1]</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr" s="3">
+      <c r="H91" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 ロッカールームから笑い声が聞こえてくる</t>
         </is>
@@ -2691,20 +3147,25 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr" s="2">
+      <c r="D92" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr" s="12">
+      <c r="E92" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">good[2]</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr" s="3">
+      <c r="H92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 控室の空気は和やかだ</t>
         </is>
@@ -2718,20 +3179,25 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr" s="2">
+      <c r="D93" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr" s="12">
+      <c r="E93" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">good[3]</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr" s="3">
+      <c r="H93" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 選手たちが自主練で残っている</t>
         </is>
@@ -2745,20 +3211,25 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr" s="2">
+      <c r="D94" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr" s="12">
+      <c r="E94" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">good[4]</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr" s="3">
+      <c r="H94" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 誰かが差し入れを持ってきたらしい</t>
         </is>
@@ -2772,20 +3243,25 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr" s="2">
+      <c r="D95" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr" s="12">
+      <c r="E95" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">warning[1]</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr" s="3">
+      <c r="H95" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 控室で{name}がため息をついていた</t>
         </is>
@@ -2799,20 +3275,25 @@
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr" s="2">
+      <c r="D96" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr" s="12">
+      <c r="E96" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">warning[2]</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr" s="3">
+      <c r="H96" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 {name}の表情が最近硬い</t>
         </is>
@@ -2826,20 +3307,25 @@
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr" s="2">
+      <c r="D97" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr" s="12">
+      <c r="E97" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">warning[3]</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr" s="3">
+      <c r="H97" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 ロッカーの会話が少ない日が続いている</t>
         </is>
@@ -2853,20 +3339,25 @@
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr" s="2">
+      <c r="D98" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr" s="12">
+      <c r="E98" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">warning[4]</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr" s="3">
+      <c r="H98" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 {name}が一人で帰る姿を見かけた</t>
         </is>
@@ -2880,20 +3371,25 @@
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr" s="2">
+      <c r="D99" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr" s="12">
+      <c r="E99" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">warning[5]</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr" s="3">
+      <c r="H99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 練習後、{name}がスマホをじっと見つめていた</t>
         </is>
@@ -2907,20 +3403,25 @@
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr" s="2">
+      <c r="D100" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr" s="12">
+      <c r="E100" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">danger[1]</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr" s="3">
+      <c r="H100" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 ロッカールームの空気が重い</t>
         </is>
@@ -2934,20 +3435,25 @@
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr" s="2">
+      <c r="D101" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr" s="12">
+      <c r="E101" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">danger[2]</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr" s="3">
+      <c r="H101" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 {name}と{name2}が何か話し込んでいた</t>
         </is>
@@ -2961,20 +3467,25 @@
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr" s="2">
+      <c r="D102" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr" s="12">
+      <c r="E102" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">danger[3]</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr" s="3">
+      <c r="H102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 控室で小さな言い争いがあったらしい</t>
         </is>
@@ -2988,20 +3499,25 @@
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr" s="2">
+      <c r="D103" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr" s="12">
+      <c r="E103" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">danger[4]</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr" s="3">
+      <c r="H103" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 {name}の機嫌が明らかに悪い</t>
         </is>
@@ -3015,20 +3531,25 @@
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr" s="2">
+      <c r="D104" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LOCKER_AIR_TEXTS</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr" s="12">
+      <c r="E104" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">danger[5]</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr" s="3">
+      <c r="H104" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 誰もが口数少なく着替えを済ませていた</t>
         </is>
@@ -3042,20 +3563,25 @@
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr" s="2">
+      <c r="D105" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr" s="12">
+      <c r="E105" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1][1].text</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr" s="3">
+      <c r="H105" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習場が静まり返っている</t>
         </is>
@@ -3069,20 +3595,25 @@
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr" s="2">
+      <c r="D106" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr" s="12">
+      <c r="E106" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1][2].text</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr" s="3">
+      <c r="H106" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">誰も目を合わせようとしない</t>
         </is>
@@ -3096,20 +3627,25 @@
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr" s="2">
+      <c r="D107" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr" s="12">
+      <c r="E107" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1][3].text</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr" s="3">
+      <c r="H107" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">重い空気が漂っている</t>
         </is>
@@ -3123,20 +3659,25 @@
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr" s="2">
+      <c r="D108" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr" s="12">
+      <c r="E108" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2][1].text</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr" s="3">
+      <c r="H108" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">どこかよそよそしい空気がある</t>
         </is>
@@ -3150,20 +3691,25 @@
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr" s="2">
+      <c r="D109" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr" s="12">
+      <c r="E109" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2][2].text</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr" s="3">
+      <c r="H109" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最低限のメニューだけこなしている</t>
         </is>
@@ -3177,20 +3723,25 @@
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr" s="2">
+      <c r="D110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="12">
+      <c r="E110" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2][3].text</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr" s="3">
+      <c r="H110" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">会話が少ない</t>
         </is>
@@ -3204,20 +3755,25 @@
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr" s="2">
+      <c r="D111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="12">
+      <c r="E111" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3][1].text</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr" s="3">
+      <c r="H111" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">淡々とメニューをこなしている</t>
         </is>
@@ -3231,20 +3787,25 @@
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr" s="2">
+      <c r="D112" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr" s="12">
+      <c r="E112" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3][2].text</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr" s="3">
+      <c r="H112" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">いつも通りの練習風景</t>
         </is>
@@ -3258,20 +3819,25 @@
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr" s="2">
+      <c r="D113" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr" s="12">
+      <c r="E113" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3][3].text</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr" s="3">
+      <c r="H113" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">特に変わった様子はない</t>
         </is>
@@ -3285,20 +3851,25 @@
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr" s="2">
+      <c r="D114" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr" s="12">
+      <c r="E114" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3][4].text</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr" s="3">
+      <c r="H114" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">黙々と汗を流している</t>
         </is>
@@ -3312,20 +3883,25 @@
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr" s="2">
+      <c r="D115" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr" s="12">
+      <c r="E115" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4][1].text</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr" s="3">
+      <c r="H115" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">声が飛び交っている</t>
         </is>
@@ -3339,20 +3915,25 @@
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr" s="2">
+      <c r="D116" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr" s="12">
+      <c r="E116" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4][2].text</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr" s="3">
+      <c r="H116" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習に熱が入っている</t>
         </is>
@@ -3366,20 +3947,25 @@
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr" s="2">
+      <c r="D117" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr" s="12">
+      <c r="E117" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4][3].text</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr" s="3">
+      <c r="H117" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手同士でアドバイスし合っている</t>
         </is>
@@ -3393,20 +3979,25 @@
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr" s="2">
+      <c r="D118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr" s="12">
+      <c r="E118" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4][4].text</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr" s="3">
+      <c r="H118" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">活気のある練習場</t>
         </is>
@@ -3420,20 +4011,25 @@
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr" s="2">
+      <c r="D119" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr" s="12">
+      <c r="E119" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5][1].text</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr" s="3">
+      <c r="H119" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">自主練する選手が増えている</t>
         </is>
@@ -3447,20 +4043,25 @@
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr" s="2">
+      <c r="D120" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr" s="12">
+      <c r="E120" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5][2].text</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr" s="3">
+      <c r="H120" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習場に笑い声が響いている</t>
         </is>
@@ -3474,20 +4075,25 @@
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr" s="2">
+      <c r="D121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
+      <c r="E121" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5][3].text</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr" s="3">
+      <c r="H121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">全員の目つきが違う</t>
         </is>
@@ -3501,20 +4107,25 @@
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr" s="2">
+      <c r="D122" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
+      <c r="E122" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5][4].text</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr" s="3">
+      <c r="H122" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">チーム全体に勢いがある</t>
         </is>
@@ -3528,25 +4139,30 @@
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.standard</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="F123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr" s="3">
+      <c r="H123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
         </is>
@@ -3560,25 +4176,30 @@
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.ojousama</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="F124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr" s="3">
+      <c r="H124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
         </is>
@@ -3592,25 +4213,30 @@
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.delinquent</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="F125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr" s="3">
+      <c r="H125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
         </is>
@@ -3624,25 +4250,30 @@
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.cool</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="F126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr" s="3">
+      <c r="H126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
         </is>
@@ -3656,25 +4287,30 @@
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.seductive</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="F127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr" s="3">
+      <c r="H127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
         </is>
@@ -3688,25 +4324,30 @@
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.polite</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="F128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr" s="3">
+      <c r="H128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
         </is>
@@ -3720,25 +4361,30 @@
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trust.composed</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr" s="2">
+      <c r="F129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr" s="3">
+      <c r="H129" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
         </is>
@@ -3752,25 +4398,30 @@
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.standard</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr" s="2">
+      <c r="F130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr" s="3">
+      <c r="H130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
         </is>
@@ -3784,25 +4435,30 @@
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.ojousama</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr" s="2">
+      <c r="F131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr" s="3">
+      <c r="H131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
         </is>
@@ -3816,25 +4472,30 @@
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.delinquent</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr" s="2">
+      <c r="F132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr" s="3">
+      <c r="H132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
         </is>
@@ -3848,25 +4509,30 @@
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.cool</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr" s="2">
+      <c r="F133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr" s="3">
+      <c r="H133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
         </is>
@@ -3880,25 +4546,30 @@
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.seductive</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr" s="2">
+      <c r="F134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr" s="3">
+      <c r="H134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
         </is>
@@ -3912,25 +4583,30 @@
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.polite</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr" s="2">
+      <c r="F135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr" s="3">
+      <c r="H135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">競い合えることが、自分の力になっています</t>
         </is>
@@ -3944,25 +4620,30 @@
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rival_friend.composed</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr" s="2">
+      <c r="F136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr" s="3">
+      <c r="H136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
         </is>
@@ -3976,25 +4657,30 @@
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.standard</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr" s="2">
+      <c r="F137" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr" s="3">
+      <c r="H137" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
         </is>
@@ -4008,25 +4694,30 @@
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.ojousama</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr" s="2">
+      <c r="F138" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr" s="3">
+      <c r="H138" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
         </is>
@@ -4040,25 +4731,30 @@
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.delinquent</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr" s="2">
+      <c r="F139" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr" s="3">
+      <c r="H139" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
         </is>
@@ -4072,25 +4768,30 @@
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.cool</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr" s="2">
+      <c r="F140" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr" s="3">
+      <c r="H140" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
         </is>
@@ -4104,25 +4805,30 @@
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.seductive</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr" s="2">
+      <c r="F141" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr" s="3">
+      <c r="H141" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
         </is>
@@ -4136,25 +4842,30 @@
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.polite</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr" s="2">
+      <c r="F142" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr" s="3">
+      <c r="H142" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
         </is>
@@ -4168,25 +4879,30 @@
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">destined_rival.composed</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr" s="2">
+      <c r="F143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr" s="3">
+      <c r="H143" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
         </is>
@@ -4200,25 +4916,30 @@
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.standard</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr" s="2">
+      <c r="F144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr" s="3">
+      <c r="H144" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
         </is>
@@ -4232,25 +4953,30 @@
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.ojousama</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr" s="2">
+      <c r="F145" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr" s="3">
+      <c r="H145" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
         </is>
@@ -4264,25 +4990,30 @@
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.delinquent</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr" s="2">
+      <c r="F146" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr" s="3">
+      <c r="H146" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
         </is>
@@ -4296,25 +5027,30 @@
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.cool</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr" s="2">
+      <c r="F147" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr" s="3">
+      <c r="H147" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
         </is>
@@ -4328,25 +5064,30 @@
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.seductive</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr" s="2">
+      <c r="F148" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr" s="3">
+      <c r="H148" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
         </is>
@@ -4360,25 +5101,30 @@
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.polite</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr" s="2">
+      <c r="F149" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr" s="3">
+      <c r="H149" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
         </is>
@@ -4392,25 +5138,30 @@
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">acquaintance.composed</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr" s="2">
+      <c r="F150" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr" s="3">
+      <c r="H150" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
         </is>
@@ -4424,25 +5175,30 @@
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.standard</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr" s="2">
+      <c r="F151" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr" s="3">
+      <c r="H151" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
         </is>
@@ -4456,25 +5212,30 @@
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.ojousama</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr" s="2">
+      <c r="F152" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr" s="3">
+      <c r="H152" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
         </is>
@@ -4488,25 +5249,30 @@
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.delinquent</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr" s="2">
+      <c r="F153" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr" s="3">
+      <c r="H153" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
         </is>
@@ -4520,25 +5286,30 @@
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.cool</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr" s="2">
+      <c r="F154" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr" s="3">
+      <c r="H154" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">気にしていないつもりだった……</t>
         </is>
@@ -4552,25 +5323,30 @@
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.seductive</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr" s="2">
+      <c r="F155" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr" s="3">
+      <c r="H155" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
         </is>
@@ -4584,25 +5360,30 @@
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.polite</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr" s="2">
+      <c r="F156" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr" s="3">
+      <c r="H156" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
         </is>
@@ -4616,25 +5397,30 @@
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">intrigued.composed</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr" s="2">
+      <c r="F157" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="3">
+      <c r="H157" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
         </is>
@@ -4648,25 +5434,30 @@
       </c>
       <c r="B158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.standard</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr" s="2">
+      <c r="F158" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr" s="3">
+      <c r="H158" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
         </is>
@@ -4680,25 +5471,30 @@
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.ojousama</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr" s="2">
+      <c r="F159" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr" s="3">
+      <c r="H159" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
         </is>
@@ -4712,25 +5508,30 @@
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.delinquent</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr" s="2">
+      <c r="F160" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr" s="3">
+      <c r="H160" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
         </is>
@@ -4744,25 +5545,30 @@
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.cool</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr" s="2">
+      <c r="F161" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr" s="3">
+      <c r="H161" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
         </is>
@@ -4776,25 +5582,30 @@
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.seductive</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr" s="2">
+      <c r="F162" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr" s="3">
+      <c r="H162" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
         </is>
@@ -4808,25 +5619,30 @@
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.polite</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr" s="2">
+      <c r="F163" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr" s="3">
+      <c r="H163" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
         </is>
@@ -4840,25 +5656,30 @@
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostile_competitor.composed</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr" s="2">
+      <c r="F164" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr" s="3">
+      <c r="H164" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
         </is>
@@ -4872,25 +5693,30 @@
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.standard</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr" s="2">
+      <c r="F165" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr" s="3">
+      <c r="H165" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
         </is>
@@ -4904,25 +5730,30 @@
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.ojousama</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr" s="2">
+      <c r="F166" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr" s="3">
+      <c r="H166" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
         </is>
@@ -4936,25 +5767,30 @@
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.delinquent</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr" s="2">
+      <c r="F167" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr" s="3">
+      <c r="H167" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あー、いたな。それで?</t>
         </is>
@@ -4968,25 +5804,30 @@
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.cool</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr" s="2">
+      <c r="F168" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr" s="3">
+      <c r="H168" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認識しているだけ。それ以上はない</t>
         </is>
@@ -5000,25 +5841,30 @@
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.seductive</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr" s="2">
+      <c r="F169" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr" s="3">
+      <c r="H169" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
         </is>
@@ -5032,25 +5878,30 @@
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.polite</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr" s="2">
+      <c r="F170" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr" s="3">
+      <c r="H170" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お見かけはしますけれど、特には……</t>
         </is>
@@ -5064,25 +5915,30 @@
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">distant.composed</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr" s="2">
+      <c r="F171" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr" s="3">
+      <c r="H171" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
         </is>
@@ -5096,25 +5952,30 @@
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.standard</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr" s="2">
+      <c r="F172" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr" s="3">
+      <c r="H172" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
         </is>
@@ -5128,25 +5989,30 @@
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.ojousama</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr" s="2">
+      <c r="F173" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr" s="3">
+      <c r="H173" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
         </is>
@@ -5160,25 +6026,30 @@
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.delinquent</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr" s="2">
+      <c r="F174" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr" s="3">
+      <c r="H174" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
         </is>
@@ -5192,25 +6063,30 @@
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.cool</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr" s="2">
+      <c r="F175" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr" s="3">
+      <c r="H175" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
         </is>
@@ -5224,25 +6100,30 @@
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.seductive</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr" s="2">
+      <c r="F176" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr" s="3">
+      <c r="H176" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
         </is>
@@ -5256,25 +6137,30 @@
       </c>
       <c r="B177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.polite</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr" s="2">
+      <c r="F177" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr" s="3">
+      <c r="H177" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
         </is>
@@ -5288,25 +6174,30 @@
       </c>
       <c r="B178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">contempt.composed</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr" s="2">
+      <c r="F178" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr" s="3">
+      <c r="H178" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
         </is>
@@ -5320,25 +6211,30 @@
       </c>
       <c r="B179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.standard</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr" s="2">
+      <c r="F179" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr" s="3">
+      <c r="H179" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
         </is>
@@ -5352,25 +6248,30 @@
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.ojousama</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr" s="2">
+      <c r="F180" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr" s="3">
+      <c r="H180" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
         </is>
@@ -5384,25 +6285,30 @@
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.delinquent</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr" s="2">
+      <c r="F181" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr" s="3">
+      <c r="H181" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
         </is>
@@ -5416,25 +6322,30 @@
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.cool</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr" s="2">
+      <c r="F182" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr" s="3">
+      <c r="H182" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">不快。距離を取りたい</t>
         </is>
@@ -5448,25 +6359,30 @@
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.seductive</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr" s="2">
+      <c r="F183" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr" s="3">
+      <c r="H183" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
         </is>
@@ -5480,25 +6396,30 @@
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.polite</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr" s="2">
+      <c r="F184" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr" s="3">
+      <c r="H184" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
         </is>
@@ -5512,25 +6433,30 @@
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">irritation.composed</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr" s="2">
+      <c r="F185" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr" s="3">
+      <c r="H185" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
         </is>
@@ -5544,25 +6470,30 @@
       </c>
       <c r="B186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.standard</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr" s="2">
+      <c r="F186" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr" s="3">
+      <c r="H186" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
         </is>
@@ -5576,25 +6507,30 @@
       </c>
       <c r="B187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.ojousama</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr" s="2">
+      <c r="F187" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr" s="3">
+      <c r="H187" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
         </is>
@@ -5608,25 +6544,30 @@
       </c>
       <c r="B188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.delinquent</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr" s="2">
+      <c r="F188" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr" s="3">
+      <c r="H188" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
         </is>
@@ -5640,25 +6581,30 @@
       </c>
       <c r="B189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.cool</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr" s="2">
+      <c r="F189" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr" s="3">
+      <c r="H189" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">受け付けない。理屈じゃない</t>
         </is>
@@ -5672,25 +6618,30 @@
       </c>
       <c r="B190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.seductive</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr" s="2">
+      <c r="F190" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr" s="3">
+      <c r="H190" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
         </is>
@@ -5704,25 +6655,30 @@
       </c>
       <c r="B191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.polite</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr" s="2">
+      <c r="F191" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr" s="3">
+      <c r="H191" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
         </is>
@@ -5736,25 +6692,30 @@
       </c>
       <c r="B192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike.composed</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr" s="2">
+      <c r="F192" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr" s="3">
+      <c r="H192" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
         </is>
@@ -5768,25 +6729,30 @@
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.standard</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr" s="2">
+      <c r="F193" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr" s="3">
+      <c r="H193" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
         </is>
@@ -5800,25 +6766,30 @@
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.ojousama</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr" s="2">
+      <c r="F194" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr" s="3">
+      <c r="H194" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
         </is>
@@ -5832,25 +6803,30 @@
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.delinquent</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr" s="2">
+      <c r="F195" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr" s="3">
+      <c r="H195" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
         </is>
@@ -5864,25 +6840,30 @@
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.cool</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr" s="2">
+      <c r="F196" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr" s="3">
+      <c r="H196" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">存在を認識から外している。話すこともない</t>
         </is>
@@ -5896,25 +6877,30 @@
       </c>
       <c r="B197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.seductive</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr" s="2">
+      <c r="F197" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr" s="3">
+      <c r="H197" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
         </is>
@@ -5928,25 +6914,30 @@
       </c>
       <c r="B198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.polite</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr" s="2">
+      <c r="F198" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr" s="3">
+      <c r="H198" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
         </is>
@@ -5960,25 +6951,30 @@
       </c>
       <c r="B199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cold_loathing.composed</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr" s="2">
+      <c r="F199" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr" s="3">
+      <c r="H199" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
         </is>
@@ -5992,25 +6988,30 @@
       </c>
       <c r="B200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.standard</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr" s="2">
+      <c r="F200" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr" s="3">
+      <c r="H200" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
         </is>
@@ -6024,25 +7025,30 @@
       </c>
       <c r="B201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.ojousama</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr" s="2">
+      <c r="F201" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr" s="3">
+      <c r="H201" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
         </is>
@@ -6056,25 +7062,30 @@
       </c>
       <c r="B202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.delinquent</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr" s="2">
+      <c r="F202" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr" s="3">
+      <c r="H202" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
         </is>
@@ -6088,25 +7099,30 @@
       </c>
       <c r="B203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.cool</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr" s="2">
+      <c r="F203" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr" s="3">
+      <c r="H203" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">生理的に駄目。これは変わらない</t>
         </is>
@@ -6120,25 +7136,30 @@
       </c>
       <c r="B204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.seductive</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr" s="2">
+      <c r="F204" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr" s="3">
+      <c r="H204" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
         </is>
@@ -6152,25 +7173,30 @@
       </c>
       <c r="B205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.polite</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr" s="2">
+      <c r="F205" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr" s="3">
+      <c r="H205" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
         </is>
@@ -6184,25 +7210,30 @@
       </c>
       <c r="B206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">dislike_strong.composed</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr" s="2">
+      <c r="F206" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr" s="3">
+      <c r="H206" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
         </is>
@@ -6216,25 +7247,30 @@
       </c>
       <c r="B207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.standard</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr" s="2">
+      <c r="F207" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr" s="3">
+      <c r="H207" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
         </is>
@@ -6248,25 +7284,30 @@
       </c>
       <c r="B208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.ojousama</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr" s="2">
+      <c r="F208" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr" s="3">
+      <c r="H208" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
         </is>
@@ -6280,25 +7321,30 @@
       </c>
       <c r="B209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.delinquent</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr" s="2">
+      <c r="F209" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr" s="3">
+      <c r="H209" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
         </is>
@@ -6312,25 +7358,30 @@
       </c>
       <c r="B210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.cool</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr" s="2">
+      <c r="F210" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">クール</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr" s="3">
+      <c r="H210" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
         </is>
@@ -6344,25 +7395,30 @@
       </c>
       <c r="B211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.seductive</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr" s="2">
+      <c r="F211" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr" s="3">
+      <c r="H211" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
         </is>
@@ -6376,25 +7432,30 @@
       </c>
       <c r="B212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.polite</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr" s="2">
+      <c r="F212" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr" s="3">
+      <c r="H212" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
         </is>
@@ -6408,25 +7469,30 @@
       </c>
       <c r="B213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">雰囲気・その他</t>
         </is>
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr" s="12">
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hatred.composed</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr" s="2">
+      <c r="F213" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr" s="3">
+      <c r="H213" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
         </is>
@@ -6440,20 +7506,25 @@
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr" s="2">
+      <c r="D214" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr" s="12">
+      <c r="E214" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1].label</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr" s="3">
+      <c r="H214" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">初興行収入</t>
         </is>
@@ -6467,20 +7538,25 @@
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr" s="2">
+      <c r="D215" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr" s="12">
+      <c r="E215" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1].desc</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr" s="3">
+      <c r="H215" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
         </is>
@@ -6494,20 +7570,25 @@
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr" s="2">
+      <c r="D216" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr" s="12">
+      <c r="E216" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2].label</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr" s="3">
+      <c r="H216" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スポンサー獲得</t>
         </is>
@@ -6521,20 +7602,25 @@
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr" s="2">
+      <c r="D217" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr" s="12">
+      <c r="E217" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2].desc</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr" s="3">
+      <c r="H217" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
         </is>
@@ -6548,20 +7634,25 @@
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr" s="2">
+      <c r="D218" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr" s="12">
+      <c r="E218" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3].label</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr" s="3">
+      <c r="H218" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">初の月次黒字</t>
         </is>
@@ -6575,20 +7666,25 @@
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr" s="2">
+      <c r="D219" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr" s="12">
+      <c r="E219" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3].desc</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr" s="3">
+      <c r="H219" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
         </is>
@@ -6602,20 +7698,25 @@
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr" s="2">
+      <c r="D220" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr" s="12">
+      <c r="E220" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4].label</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr" s="3">
+      <c r="H220" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2ヶ月連続月次黒字</t>
         </is>
@@ -6629,20 +7730,25 @@
       </c>
       <c r="B221" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr" s="2">
+      <c r="D221" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr" s="12">
+      <c r="E221" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4].desc</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr" s="3">
+      <c r="H221" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">安定経営が見えてきた</t>
         </is>
@@ -6656,20 +7762,25 @@
       </c>
       <c r="B222" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr" s="2">
+      <c r="D222" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr" s="12">
+      <c r="E222" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5].label</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr" s="3">
+      <c r="H222" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">経営安定化</t>
         </is>
@@ -6683,27 +7794,32 @@
       </c>
       <c r="B223" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr" s="2">
+      <c r="D223" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr" s="12">
+      <c r="E223" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5].desc</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr" s="3">
+      <c r="H223" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">月次黒字定着＋資金確保！サバイバルクリア</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I223"/>
+  <autoFilter ref="A1:J223"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
+++ b/セリフ編集/ナレーション・記事/雰囲気・その他.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J287"/>
+  <dimension ref="A1:J302"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5702,7 +5702,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][1].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][4].text</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5722,19 +5722,19 @@
       </c>
       <c r="E172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][1].text</t>
+          <t xml:space="preserve">[1][4].text</t>
         </is>
       </c>
       <c r="H172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこかよそよそしい空気がある</t>
+          <t xml:space="preserve">リングに上がる者がいない</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][2].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][5].text</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5754,19 +5754,19 @@
       </c>
       <c r="E173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][2].text</t>
+          <t xml:space="preserve">[1][5].text</t>
         </is>
       </c>
       <c r="H173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最低限のメニューだけこなしている</t>
+          <t xml:space="preserve">掛け声ひとつ上がらない</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][3].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[1][6].text</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5786,19 +5786,19 @@
       </c>
       <c r="E174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2][3].text</t>
+          <t xml:space="preserve">[1][6].text</t>
         </is>
       </c>
       <c r="H174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">会話が少ない</t>
+          <t xml:space="preserve">マットに汗の跡がない</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][1].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][1].text</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5818,19 +5818,19 @@
       </c>
       <c r="E175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][1].text</t>
+          <t xml:space="preserve">[2][1].text</t>
         </is>
       </c>
       <c r="H175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">淡々とメニューをこなしている</t>
+          <t xml:space="preserve">どこかよそよそしい空気がある</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][2].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][2].text</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5850,19 +5850,19 @@
       </c>
       <c r="E176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][2].text</t>
+          <t xml:space="preserve">[2][2].text</t>
         </is>
       </c>
       <c r="H176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りの練習風景</t>
+          <t xml:space="preserve">最低限のメニューだけこなしている</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][3].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][3].text</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5882,19 +5882,19 @@
       </c>
       <c r="E177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][3].text</t>
+          <t xml:space="preserve">[2][3].text</t>
         </is>
       </c>
       <c r="H177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特に変わった様子はない</t>
+          <t xml:space="preserve">会話が少ない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][4].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][4].text</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="E178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3][4].text</t>
+          <t xml:space="preserve">[2][4].text</t>
         </is>
       </c>
       <c r="H178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙々と汗を流している</t>
+          <t xml:space="preserve">時計を気にする選手が目につく</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][1].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][5].text</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5946,19 +5946,19 @@
       </c>
       <c r="E179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][1].text</t>
+          <t xml:space="preserve">[2][5].text</t>
         </is>
       </c>
       <c r="H179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声が飛び交っている</t>
+          <t xml:space="preserve">休憩が長引きがちだ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][2].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[2][6].text</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5978,19 +5978,19 @@
       </c>
       <c r="E180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][2].text</t>
+          <t xml:space="preserve">[2][6].text</t>
         </is>
       </c>
       <c r="H180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習に熱が入っている</t>
+          <t xml:space="preserve">組む相手を決めるのに手間取っている</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][3].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][1].text</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6010,19 +6010,19 @@
       </c>
       <c r="E181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][3].text</t>
+          <t xml:space="preserve">[3][1].text</t>
         </is>
       </c>
       <c r="H181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手同士でアドバイスし合っている</t>
+          <t xml:space="preserve">淡々とメニューをこなしている</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][4].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][2].text</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6042,19 +6042,19 @@
       </c>
       <c r="E182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4][4].text</t>
+          <t xml:space="preserve">[3][2].text</t>
         </is>
       </c>
       <c r="H182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活気のある練習場</t>
+          <t xml:space="preserve">いつも通りの練習風景</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][1].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][3].text</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6074,19 +6074,19 @@
       </c>
       <c r="E183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][1].text</t>
+          <t xml:space="preserve">[3][3].text</t>
         </is>
       </c>
       <c r="H183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自主練する選手が増えている</t>
+          <t xml:space="preserve">特に変わった様子はない</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][2].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][4].text</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6106,19 +6106,19 @@
       </c>
       <c r="E184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][2].text</t>
+          <t xml:space="preserve">[3][4].text</t>
         </is>
       </c>
       <c r="H184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習場に笑い声が響いている</t>
+          <t xml:space="preserve">黙々と汗を流している</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][3].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][5].text</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6138,19 +6138,19 @@
       </c>
       <c r="E185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][3].text</t>
+          <t xml:space="preserve">[3][5].text</t>
         </is>
       </c>
       <c r="H185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員の目つきが違う</t>
+          <t xml:space="preserve">受け身の音が規則正しく響いている</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][4].text</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][6].text</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6170,19 +6170,19 @@
       </c>
       <c r="E186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5][4].text</t>
+          <t xml:space="preserve">[3][6].text</t>
         </is>
       </c>
       <c r="H186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チーム全体に勢いがある</t>
+          <t xml:space="preserve">定刻通りに始まり、定刻通りに終わる</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.standard</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[3][7].text</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6192,34 +6192,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.standard</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">[3][7].text</t>
         </is>
       </c>
       <c r="H187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
+          <t xml:space="preserve">汗を拭いては、また組み直している</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.ojousama</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][1].text</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6229,34 +6224,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.ojousama</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">[4][1].text</t>
         </is>
       </c>
       <c r="H188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
+          <t xml:space="preserve">声が飛び交っている</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.delinquent</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][2].text</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6266,34 +6256,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.delinquent</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">[4][2].text</t>
         </is>
       </c>
       <c r="H189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
+          <t xml:space="preserve">練習に熱が入っている</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.cool</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][3].text</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6303,34 +6288,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.cool</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">[4][3].text</t>
         </is>
       </c>
       <c r="H190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
+          <t xml:space="preserve">選手同士でアドバイスし合っている</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.seductive</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][4].text</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6340,34 +6320,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.seductive</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">[4][4].text</t>
         </is>
       </c>
       <c r="H191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
+          <t xml:space="preserve">活気のある練習場</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.polite</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][5].text</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6377,34 +6352,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.polite</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[4][5].text</t>
         </is>
       </c>
       <c r="H192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
+          <t xml:space="preserve">順番待ちの列ができている</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.trust.composed</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][6].text</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6414,34 +6384,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust.composed</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[4][6].text</t>
         </is>
       </c>
       <c r="H193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
+          <t xml:space="preserve">ロープの鳴る音が途切れない</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.standard</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[4][7].text</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6451,34 +6416,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.standard</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">[4][7].text</t>
         </is>
       </c>
       <c r="H194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
+          <t xml:space="preserve">息が上がっても手を止めない</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.ojousama</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][1].text</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6488,34 +6448,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.ojousama</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">[5][1].text</t>
         </is>
       </c>
       <c r="H195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
+          <t xml:space="preserve">自主練する選手が増えている</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.delinquent</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][2].text</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6525,34 +6480,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.delinquent</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">[5][2].text</t>
         </is>
       </c>
       <c r="H196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
+          <t xml:space="preserve">練習場に笑い声が響いている</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.cool</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][3].text</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6562,34 +6512,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.cool</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">[5][3].text</t>
         </is>
       </c>
       <c r="H197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
+          <t xml:space="preserve">全員の目つきが違う</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.seductive</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][4].text</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6599,34 +6544,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.seductive</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">[5][4].text</t>
         </is>
       </c>
       <c r="H198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
+          <t xml:space="preserve">チーム全体に勢いがある</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.polite</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][5].text</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6636,34 +6576,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.polite</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">[5][5].text</t>
         </is>
       </c>
       <c r="H199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">競い合えることが、自分の力になっています</t>
+          <t xml:space="preserve">消灯の時間を過ぎても人が残っている</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.composed</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][6].text</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6673,34 +6608,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rival_friend.composed</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">[5][6].text</t>
         </is>
       </c>
       <c r="H200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
+          <t xml:space="preserve">終わりの合図を誰も聞いていない</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.standard</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS[5][7].text</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6710,34 +6640,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/ui-render.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS</t>
+          <t xml:space="preserve">ATMOSPHERE_TEXTS</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.standard</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">[5][7].text</t>
         </is>
       </c>
       <c r="H201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
+          <t xml:space="preserve">マットが汗で滑るほど濡れている</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.standard</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6757,24 +6682,24 @@
       </c>
       <c r="E202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.ojousama</t>
+          <t xml:space="preserve">trust.standard</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
+          <t xml:space="preserve">そばにいてくれるだけで、なんだか安心する</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.ojousama</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6794,24 +6719,24 @@
       </c>
       <c r="E203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.delinquent</t>
+          <t xml:space="preserve">trust.ojousama</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
+          <t xml:space="preserve">お隣にいてくださると、心が穏やかになりますの</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.delinquent</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6831,24 +6756,24 @@
       </c>
       <c r="E204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.cool</t>
+          <t xml:space="preserve">trust.delinquent</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
+          <t xml:space="preserve">一緒にいると……なんか、落ち着くんだよな</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.cool</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6868,24 +6793,24 @@
       </c>
       <c r="E205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.seductive</t>
+          <t xml:space="preserve">trust.cool</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
+          <t xml:space="preserve">信頼できる数少ない人間。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.seductive</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6905,24 +6830,24 @@
       </c>
       <c r="E206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.polite</t>
+          <t xml:space="preserve">trust.seductive</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
+          <t xml:space="preserve">隣にいると、居心地がいいのよね……ふふ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.polite</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6942,24 +6867,24 @@
       </c>
       <c r="E207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">destined_rival.composed</t>
+          <t xml:space="preserve">trust.polite</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
+          <t xml:space="preserve">本当に感謝しています。大切な存在です</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.trust.composed</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6979,24 +6904,24 @@
       </c>
       <c r="E208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.standard</t>
+          <t xml:space="preserve">trust.composed</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
+          <t xml:space="preserve">一緒にいてくれると、不思議と心が落ち着くのよね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.standard</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7016,24 +6941,24 @@
       </c>
       <c r="E209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.ojousama</t>
+          <t xml:space="preserve">rival_friend.standard</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
+          <t xml:space="preserve">負けたくない。でも、おかげで強くなれている気がする</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.ojousama</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7053,24 +6978,24 @@
       </c>
       <c r="E210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.delinquent</t>
+          <t xml:space="preserve">rival_friend.ojousama</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
+          <t xml:space="preserve">負けたくありませんけれど……実力は認めざるを得ませんわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.delinquent</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7090,24 +7015,24 @@
       </c>
       <c r="E211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.cool</t>
+          <t xml:space="preserve">rival_friend.delinquent</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
+          <t xml:space="preserve">ぜってー負けねえ。でもまあ……いるから燃えんだよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.cool</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7127,24 +7052,24 @@
       </c>
       <c r="E212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.seductive</t>
+          <t xml:space="preserve">rival_friend.cool</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
+          <t xml:space="preserve">互いに高め合える関係。……悪くない</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.seductive</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7164,24 +7089,24 @@
       </c>
       <c r="E213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.polite</t>
+          <t xml:space="preserve">rival_friend.seductive</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
+          <t xml:space="preserve">勝ちたい……でも、追いかけてる時間も嫌いじゃないの</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.polite</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7201,24 +7126,24 @@
       </c>
       <c r="E214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">acquaintance.composed</t>
+          <t xml:space="preserve">rival_friend.polite</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
+          <t xml:space="preserve">競い合えることが、自分の力になっています</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.rival_friend.composed</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7238,24 +7163,24 @@
       </c>
       <c r="E215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.standard</t>
+          <t xml:space="preserve">rival_friend.composed</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
+          <t xml:space="preserve">あの子のおかげで、わたくしも頑張れるの。ありがたい存在ね</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.standard</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7275,24 +7200,24 @@
       </c>
       <c r="E216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.ojousama</t>
+          <t xml:space="preserve">destined_rival.standard</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
+          <t xml:space="preserve">考えない日はない。絶対に、越えなきゃいけない壁</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.ojousama</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7312,24 +7237,24 @@
       </c>
       <c r="E217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.delinquent</t>
+          <t xml:space="preserve">destined_rival.ojousama</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
+          <t xml:space="preserve">何があっても……わたくしの手で超えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.delinquent</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7349,24 +7274,24 @@
       </c>
       <c r="E218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.cool</t>
+          <t xml:space="preserve">destined_rival.delinquent</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気にしていないつもりだった……</t>
+          <t xml:space="preserve">四六時中頭ん中にいやがる。絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.cool</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7386,24 +7311,24 @@
       </c>
       <c r="E219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.seductive</t>
+          <t xml:space="preserve">destined_rival.cool</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
+          <t xml:space="preserve">……いなければ、今の自分はいない。だからこそ、倒す</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.seductive</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7423,24 +7348,24 @@
       </c>
       <c r="E220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.polite</t>
+          <t xml:space="preserve">destined_rival.seductive</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
+          <t xml:space="preserve">頭から離れない……悔しいけど、そういうことなのよね</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.intrigued.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.polite</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7460,24 +7385,24 @@
       </c>
       <c r="E221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">intrigued.composed</t>
+          <t xml:space="preserve">destined_rival.polite</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
+          <t xml:space="preserve">その存在が、私を突き動かしています。必ず、超えてみせます</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.destined_rival.composed</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7497,24 +7422,24 @@
       </c>
       <c r="E222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.standard</t>
+          <t xml:space="preserve">destined_rival.composed</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
+          <t xml:space="preserve">あの子とはいつか、決着をつけなければね。楽しみでもあるのよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.standard</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7534,24 +7459,24 @@
       </c>
       <c r="E223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.ojousama</t>
+          <t xml:space="preserve">acquaintance.standard</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
+          <t xml:space="preserve">まあ、知ってはいるけど……それだけかな</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.ojousama</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7571,24 +7496,24 @@
       </c>
       <c r="E224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.delinquent</t>
+          <t xml:space="preserve">acquaintance.ojousama</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、特別な感情はございませんわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.delinquent</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7608,24 +7533,24 @@
       </c>
       <c r="E225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.cool</t>
+          <t xml:space="preserve">acquaintance.delinquent</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
+          <t xml:space="preserve">あー、いたな。別にどうでもいいけど</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.cool</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7645,24 +7570,24 @@
       </c>
       <c r="E226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.seductive</t>
+          <t xml:space="preserve">acquaintance.cool</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
+          <t xml:space="preserve">認識はしている。それ以上でもそれ以下でもない</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.seductive</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7682,24 +7607,24 @@
       </c>
       <c r="E227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.polite</t>
+          <t xml:space="preserve">acquaintance.seductive</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
+          <t xml:space="preserve">知ってるわよ、一応ね。……それだけ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.polite</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7719,24 +7644,24 @@
       </c>
       <c r="E228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostile_competitor.composed</t>
+          <t xml:space="preserve">acquaintance.polite</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
+          <t xml:space="preserve">お名前は存じています。お話する機会は少ないですけれど</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.acquaintance.composed</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7756,24 +7681,24 @@
       </c>
       <c r="E229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.standard</t>
+          <t xml:space="preserve">acquaintance.composed</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
+          <t xml:space="preserve">そうねぇ、お名前くらいは存じているかしら</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.standard</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7793,24 +7718,24 @@
       </c>
       <c r="E230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.ojousama</t>
+          <t xml:space="preserve">intrigued.standard</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
+          <t xml:space="preserve">なんだろう、目で追ってしまう。気にしてないと言えば嘘になる</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.ojousama</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7830,24 +7755,24 @@
       </c>
       <c r="E231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.delinquent</t>
+          <t xml:space="preserve">intrigued.ojousama</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いたな。それで?</t>
+          <t xml:space="preserve">なぜかしら……気にかかって仕方がありませんの</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.delinquent</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7867,24 +7792,24 @@
       </c>
       <c r="E232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.cool</t>
+          <t xml:space="preserve">intrigued.delinquent</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認識しているだけ。それ以上はない</t>
+          <t xml:space="preserve">……別に気にしてねーし。してねーけど、目に入んだよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.cool</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7904,24 +7829,24 @@
       </c>
       <c r="E233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.seductive</t>
+          <t xml:space="preserve">intrigued.cool</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
+          <t xml:space="preserve">気にしていないつもりだった……</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.seductive</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7941,24 +7866,24 @@
       </c>
       <c r="E234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.polite</t>
+          <t xml:space="preserve">intrigued.seductive</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますけれど、特には……</t>
+          <t xml:space="preserve">ちょっと気になるのよね……何がとは言えないけど</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.distant.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.polite</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7978,24 +7903,24 @@
       </c>
       <c r="E235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">distant.composed</t>
+          <t xml:space="preserve">intrigued.polite</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
+          <t xml:space="preserve">つい気にかけてしまいます。理由はよくわかりませんが</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.intrigued.composed</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -8015,24 +7940,24 @@
       </c>
       <c r="E236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.standard</t>
+          <t xml:space="preserve">intrigued.composed</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
+          <t xml:space="preserve">どういうわけか、あの子のことが気になるのよね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.standard</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8052,24 +7977,24 @@
       </c>
       <c r="E237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.ojousama</t>
+          <t xml:space="preserve">hostile_competitor.standard</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
+          <t xml:space="preserve">負けたくない。それだけは、はっきりしている</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.ojousama</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8089,24 +8014,24 @@
       </c>
       <c r="E238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.delinquent</t>
+          <t xml:space="preserve">hostile_competitor.ojousama</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
+          <t xml:space="preserve">絶対に遅れを取りたくありませんの。それだけですわ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.delinquent</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8126,24 +8051,24 @@
       </c>
       <c r="E239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.cool</t>
+          <t xml:space="preserve">hostile_competitor.delinquent</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
+          <t xml:space="preserve">負けねえ。死んでも負けねえ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.cool</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8163,24 +8088,24 @@
       </c>
       <c r="E240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.seductive</t>
+          <t xml:space="preserve">hostile_competitor.cool</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
+          <t xml:space="preserve">負けるわけにはいかない。理屈じゃない</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.seductive</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8200,24 +8125,24 @@
       </c>
       <c r="E241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.polite</t>
+          <t xml:space="preserve">hostile_competitor.seductive</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
+          <t xml:space="preserve">負けたくないの。理由なんて知らないわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.contempt.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.polite</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8237,24 +8162,24 @@
       </c>
       <c r="E242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">contempt.composed</t>
+          <t xml:space="preserve">hostile_competitor.polite</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
+          <t xml:space="preserve">どうしても負けたくないんです。強い気持ちがあります</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hostile_competitor.composed</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8274,24 +8199,24 @@
       </c>
       <c r="E243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.standard</t>
+          <t xml:space="preserve">hostile_competitor.composed</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
+          <t xml:space="preserve">負けるわけにはいかないわ。穏やかに、でも譲らない</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.standard</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8311,24 +8236,24 @@
       </c>
       <c r="E244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.ojousama</t>
+          <t xml:space="preserve">distant.standard</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
+          <t xml:space="preserve">名前は知ってるけど、それ以上は別に</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.ojousama</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8348,24 +8273,24 @@
       </c>
       <c r="E245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.delinquent</t>
+          <t xml:space="preserve">distant.ojousama</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、それ以上は……特に</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.delinquent</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8385,24 +8310,24 @@
       </c>
       <c r="E246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.cool</t>
+          <t xml:space="preserve">distant.delinquent</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不快。距離を取りたい</t>
+          <t xml:space="preserve">あー、いたな。それで?</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.cool</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8422,24 +8347,24 @@
       </c>
       <c r="E247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.seductive</t>
+          <t xml:space="preserve">distant.cool</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
+          <t xml:space="preserve">認識しているだけ。それ以上はない</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.seductive</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8459,24 +8384,24 @@
       </c>
       <c r="E248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.polite</t>
+          <t xml:space="preserve">distant.seductive</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
+          <t xml:space="preserve">いたわね、そういえば。……それだけ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.irritation.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.polite</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8496,24 +8421,24 @@
       </c>
       <c r="E249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">irritation.composed</t>
+          <t xml:space="preserve">distant.polite</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
+          <t xml:space="preserve">お見かけはしますけれど、特には……</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.distant.composed</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8533,24 +8458,24 @@
       </c>
       <c r="E250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.standard</t>
+          <t xml:space="preserve">distant.composed</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
+          <t xml:space="preserve">お顔は存じているわ。それだけのことね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.standard</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8570,24 +8495,24 @@
       </c>
       <c r="E251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.ojousama</t>
+          <t xml:space="preserve">contempt.standard</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
+          <t xml:space="preserve">同じリングに立っていい相手じゃない</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.ojousama</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8607,24 +8532,24 @@
       </c>
       <c r="E252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.delinquent</t>
+          <t xml:space="preserve">contempt.ojousama</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
+          <t xml:space="preserve">わたくしと並ぶには、まだ早うございますわ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.delinquent</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8644,24 +8569,24 @@
       </c>
       <c r="E253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.cool</t>
+          <t xml:space="preserve">contempt.delinquent</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受け付けない。理屈じゃない</t>
+          <t xml:space="preserve">ハッ、雑魚が視界に入んな。場違いだ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.cool</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8681,24 +8606,24 @@
       </c>
       <c r="E254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.seductive</t>
+          <t xml:space="preserve">contempt.cool</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
+          <t xml:space="preserve">実力差は数字で出てる。語ることもない</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.seductive</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8718,24 +8643,24 @@
       </c>
       <c r="E255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.polite</t>
+          <t xml:space="preserve">contempt.seductive</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
+          <t xml:space="preserve">あらあら……まだそのレベルなのね。可愛いこと</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.polite</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8755,24 +8680,24 @@
       </c>
       <c r="E256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike.composed</t>
+          <t xml:space="preserve">contempt.polite</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
+          <t xml:space="preserve">……失礼ですが、同じ土俵という気にはなれません</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.contempt.composed</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8792,24 +8717,24 @@
       </c>
       <c r="E257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.standard</t>
+          <t xml:space="preserve">contempt.composed</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
+          <t xml:space="preserve">同じ場に立つ相手だとは、思っていないの。ごめんなさいね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.standard</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8829,24 +8754,24 @@
       </c>
       <c r="E258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.ojousama</t>
+          <t xml:space="preserve">irritation.standard</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
+          <t xml:space="preserve">視界に入るたび、地味にイラっとくる</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.ojousama</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8866,24 +8791,24 @@
       </c>
       <c r="E259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.delinquent</t>
+          <t xml:space="preserve">irritation.ojousama</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
+          <t xml:space="preserve">どうにも、お顔を拝見するだけで気が立ちますの</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.delinquent</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8903,24 +8828,24 @@
       </c>
       <c r="E260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.cool</t>
+          <t xml:space="preserve">irritation.delinquent</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存在を認識から外している。話すこともない</t>
+          <t xml:space="preserve">チッ……顔見るだけでイライラすんだよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.cool</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8940,24 +8865,24 @@
       </c>
       <c r="E261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.seductive</t>
+          <t xml:space="preserve">irritation.cool</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
+          <t xml:space="preserve">不快。距離を取りたい</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.seductive</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8977,24 +8902,24 @@
       </c>
       <c r="E262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.polite</t>
+          <t xml:space="preserve">irritation.seductive</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
+          <t xml:space="preserve">なんかね、無性にカチンとくるのよ。理由は知らない</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.polite</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -9014,24 +8939,24 @@
       </c>
       <c r="E263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cold_loathing.composed</t>
+          <t xml:space="preserve">irritation.polite</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
+          <t xml:space="preserve">……正直、近くにいられると気が休まりません</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.irritation.composed</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -9051,24 +8976,24 @@
       </c>
       <c r="E264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.standard</t>
+          <t xml:space="preserve">irritation.composed</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
+          <t xml:space="preserve">あの子とは、どうしてもそりが合わないの。困ったことに</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.standard</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -9088,24 +9013,24 @@
       </c>
       <c r="E265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.ojousama</t>
+          <t xml:space="preserve">dislike.standard</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
+          <t xml:space="preserve">はっきり言って、好きじゃない。関わりたくもない</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.ojousama</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -9125,24 +9050,24 @@
       </c>
       <c r="E266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.delinquent</t>
+          <t xml:space="preserve">dislike.ojousama</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
+          <t xml:space="preserve">あの方とは、お話する気にもなれませんの</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.delinquent</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -9162,24 +9087,24 @@
       </c>
       <c r="E267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.cool</t>
+          <t xml:space="preserve">dislike.delinquent</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">生理的に駄目。これは変わらない</t>
+          <t xml:space="preserve">嫌い。マジで嫌い。それだけ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.cool</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9199,24 +9124,24 @@
       </c>
       <c r="E268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.seductive</t>
+          <t xml:space="preserve">dislike.cool</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
+          <t xml:space="preserve">受け付けない。理屈じゃない</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.seductive</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9236,24 +9161,24 @@
       </c>
       <c r="E269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.polite</t>
+          <t xml:space="preserve">dislike.seductive</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
+          <t xml:space="preserve">ごめんなさいね、あの子は無理。生理的に</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.polite</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9273,24 +9198,24 @@
       </c>
       <c r="E270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">dislike_strong.composed</t>
+          <t xml:space="preserve">dislike.polite</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
+          <t xml:space="preserve">……申し訳ありませんが、お近づきになりたくはありません</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.standard</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike.composed</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9310,24 +9235,24 @@
       </c>
       <c r="E271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.standard</t>
+          <t xml:space="preserve">dislike.composed</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
+          <t xml:space="preserve">あの子のことは、はっきりと苦手ね。隠す気もないわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.ojousama</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.standard</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9347,24 +9272,24 @@
       </c>
       <c r="E272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.ojousama</t>
+          <t xml:space="preserve">cold_loathing.standard</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
+          <t xml:space="preserve">視線も合わせない。いないものとして扱ってる</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.delinquent</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.ojousama</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9384,24 +9309,24 @@
       </c>
       <c r="E273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.delinquent</t>
+          <t xml:space="preserve">cold_loathing.ojousama</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
+          <t xml:space="preserve">わたくしの視界には、入れておりませんの</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.cool</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.delinquent</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9421,24 +9346,24 @@
       </c>
       <c r="E274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.cool</t>
+          <t xml:space="preserve">cold_loathing.delinquent</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
+          <t xml:space="preserve">……あいつは、いねえもんとして扱ってる</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.seductive</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.cool</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9458,24 +9383,24 @@
       </c>
       <c r="E275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.seductive</t>
+          <t xml:space="preserve">cold_loathing.cool</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
+          <t xml:space="preserve">存在を認識から外している。話すこともない</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.polite</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.seductive</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9495,24 +9420,24 @@
       </c>
       <c r="E276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.polite</t>
+          <t xml:space="preserve">cold_loathing.seductive</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
+          <t xml:space="preserve">あら、誰のこと？……ふふ、知らない人だわ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EMOTION_TEXTS.hatred.composed</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.polite</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9532,24 +9457,24 @@
       </c>
       <c r="E277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hatred.composed</t>
+          <t xml:space="preserve">cold_loathing.polite</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
+          <t xml:space="preserve">お話できることは、何もございません。失礼します</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[1].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.cold_loathing.composed</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9559,29 +9484,34 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].label</t>
+          <t xml:space="preserve">cold_loathing.composed</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">初興行収入</t>
+          <t xml:space="preserve">あの子のことは、わたくしの中では終わっているの</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[1].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.standard</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9591,29 +9521,34 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1].desc</t>
+          <t xml:space="preserve">dislike_strong.standard</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
+          <t xml:space="preserve">顔も見たくない。同じ空気を吸いたくない</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[2].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.ojousama</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9623,29 +9558,34 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].label</t>
+          <t xml:space="preserve">dislike_strong.ojousama</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スポンサー獲得</t>
+          <t xml:space="preserve">同じ空間にいるだけで、息が詰まりますの</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[2].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.delinquent</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9655,29 +9595,34 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2].desc</t>
+          <t xml:space="preserve">dislike_strong.delinquent</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
+          <t xml:space="preserve">マジで無理。視界から消えてくれ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[3].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.cool</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9687,29 +9632,34 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].label</t>
+          <t xml:space="preserve">dislike_strong.cool</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">初の月次黒字</t>
+          <t xml:space="preserve">生理的に駄目。これは変わらない</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[3].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.seductive</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9719,29 +9669,34 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3].desc</t>
+          <t xml:space="preserve">dislike_strong.seductive</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
+          <t xml:space="preserve">ねえ、近寄らないでくれる？……本気で</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[4].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.polite</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9751,29 +9706,34 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].label</t>
+          <t xml:space="preserve">dislike_strong.polite</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2ヶ月連続月次黒字</t>
+          <t xml:space="preserve">……同じ場にいるだけで、耐えがたいのです</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[4].desc</t>
+          <t xml:space="preserve">EMOTION_TEXTS.dislike_strong.composed</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9783,29 +9743,34 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4].desc</t>
+          <t xml:space="preserve">dislike_strong.composed</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">安定経営が見えてきた</t>
+          <t xml:space="preserve">同じ部屋にいるのも辛いの。本当に、無理なのよ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES[5].label</t>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.standard</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9815,59 +9780,574 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/app.js</t>
+          <t xml:space="preserve">src/ui-render.js</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5].label</t>
+          <t xml:space="preserve">hatred.standard</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">経営安定化</t>
+          <t xml:space="preserve">絶対に許さない。叩き潰すまで終わらない</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.ojousama</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.ojousama</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの方だけは、決して許しませんわ。何があっても</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.delinquent</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.delinquent</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ぶっ潰す。マジでぶっ潰す。それしかねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.cool</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.cool</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">消したい。自覚している。そういう感情だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.seductive</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.seductive</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この気持ち、一生消えないと思う。許す気もないし</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.polite</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.polite</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あの方のことは、生涯、許すつもりはございません</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS.hatred.composed</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/ui-render.js</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMOTION_TEXTS</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">hatred.composed</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子だけは、どうしても許せないの。穏やかではいられないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[1].label</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[1].label</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">初興行収入</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[1].desc</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[1].desc</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">興行でチケット・グッズ収入を得た</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[2].label</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[2].label</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">スポンサー獲得</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[2].desc</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[2].desc</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">人気20到達でスポンサー収入が発生</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[3].label</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[3].label</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">初の月次黒字</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[3].desc</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[3].desc</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">直近4週の合計収支がプラスになった</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[4].label</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[4].label</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2ヶ月連続月次黒字</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[4].desc</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[4].desc</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">安定経営が見えてきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES[5].label</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/app.js</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SURVIVAL_MILESTONES</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">[5].label</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">経営安定化</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES[5].desc</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">雰囲気・その他</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr" s="2">
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">雰囲気・その他</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">src/app.js</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr" s="2">
+      <c r="D302" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SURVIVAL_MILESTONES</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr" s="12">
+      <c r="E302" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5].desc</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr" s="3">
+      <c r="H302" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">月次黒字定着＋資金確保！サバイバルクリア</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J287"/>
+  <autoFilter ref="A1:J302"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
